--- a/Surveys/Survey Lines/Survey Lines.xlsx
+++ b/Surveys/Survey Lines/Survey Lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/Survey Lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{EE423639-233B-4791-B77F-F82BF1D43694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE09F10-B71E-471A-A71A-3F967255F37C}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{EE423639-233B-4791-B77F-F82BF1D43694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE12C29-40AF-4AE5-BFD0-3A76CB22B02D}"/>
   <bookViews>
-    <workbookView xWindow="-35690" yWindow="1560" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35390" yWindow="1490" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Entry" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="47">
   <si>
     <t>INSTRUCTIONS:</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>German Bank</t>
+  </si>
+  <si>
+    <t>V7</t>
   </si>
 </sst>
 </file>
@@ -620,7 +623,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -956,49 +959,49 @@
         <v>4334</v>
       </c>
       <c r="C12" s="16">
-        <v>6619.4666666666662</v>
+        <v>6615.7818181818175</v>
       </c>
       <c r="D12" s="16">
         <v>4314</v>
       </c>
       <c r="E12" s="16">
-        <v>6619.4666666666662</v>
+        <v>6615.7818181818175</v>
       </c>
       <c r="F12" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G12" s="12">
-        <v>-66.324444444444495</v>
+        <v>-66.263030303030334</v>
       </c>
       <c r="H12" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I12" s="12">
-        <v>-66.324444444444495</v>
+        <v>-66.263030303030334</v>
       </c>
       <c r="L12" s="6">
         <v>4330.12</v>
       </c>
       <c r="M12" s="6">
-        <v>6613.8</v>
+        <v>6608.76</v>
       </c>
       <c r="N12" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O12" s="6">
-        <v>6613.8</v>
+        <v>6608.76</v>
       </c>
       <c r="P12" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q12" s="6">
-        <v>-66.23</v>
+        <v>-66.146000000000001</v>
       </c>
       <c r="R12" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S12" s="6">
-        <v>-66.23</v>
+        <v>-66.146000000000001</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -1012,49 +1015,49 @@
         <v>4334</v>
       </c>
       <c r="C13" s="16">
-        <v>6624.5333333333328</v>
+        <v>6617.1636363636353</v>
       </c>
       <c r="D13" s="16">
         <v>4314</v>
       </c>
       <c r="E13" s="16">
-        <v>6624.5333333333328</v>
+        <v>6617.1636363636353</v>
       </c>
       <c r="F13" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G13" s="12">
-        <v>-66.408888888888839</v>
+        <v>-66.286060606060673</v>
       </c>
       <c r="H13" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I13" s="12">
-        <v>-66.408888888888839</v>
+        <v>-66.286060606060673</v>
       </c>
       <c r="L13" s="6">
         <v>4330.12</v>
       </c>
       <c r="M13" s="6">
-        <v>6620.1</v>
+        <v>6610.02</v>
       </c>
       <c r="N13" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O13" s="6">
-        <v>6620.1</v>
+        <v>6610.02</v>
       </c>
       <c r="P13" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q13" s="6">
-        <v>-66.334999999999994</v>
+        <v>-66.167000000000002</v>
       </c>
       <c r="R13" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S13" s="6">
-        <v>-66.334999999999994</v>
+        <v>-66.167000000000002</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -1068,49 +1071,49 @@
         <v>4334</v>
       </c>
       <c r="C14" s="16">
-        <v>6629.5999999999995</v>
+        <v>6618.5454545454531</v>
       </c>
       <c r="D14" s="16">
         <v>4314</v>
       </c>
       <c r="E14" s="16">
-        <v>6629.5999999999995</v>
+        <v>6618.5454545454531</v>
       </c>
       <c r="F14" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G14" s="12">
-        <v>-66.493333333333339</v>
+        <v>-66.309090909090827</v>
       </c>
       <c r="H14" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I14" s="12">
-        <v>-66.493333333333339</v>
+        <v>-66.309090909090827</v>
       </c>
       <c r="L14" s="6">
         <v>4330.12</v>
       </c>
       <c r="M14" s="6">
-        <v>6626.4000000000005</v>
+        <v>6611.2800000000007</v>
       </c>
       <c r="N14" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O14" s="6">
-        <v>6626.4000000000005</v>
+        <v>6611.2800000000007</v>
       </c>
       <c r="P14" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q14" s="6">
-        <v>-66.44</v>
+        <v>-66.188000000000002</v>
       </c>
       <c r="R14" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S14" s="6">
-        <v>-66.44</v>
+        <v>-66.188000000000002</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -1124,49 +1127,49 @@
         <v>4334</v>
       </c>
       <c r="C15" s="16">
-        <v>6634.6666666666661</v>
+        <v>6619.927272727271</v>
       </c>
       <c r="D15" s="16">
         <v>4314</v>
       </c>
       <c r="E15" s="16">
-        <v>6634.6666666666661</v>
+        <v>6619.927272727271</v>
       </c>
       <c r="F15" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G15" s="12">
-        <v>-66.57777777777784</v>
+        <v>-66.332121212121166</v>
       </c>
       <c r="H15" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I15" s="12">
-        <v>-66.57777777777784</v>
+        <v>-66.332121212121166</v>
       </c>
       <c r="L15" s="6">
         <v>4330.12</v>
       </c>
       <c r="M15" s="6">
-        <v>6632.7000000000007</v>
+        <v>6612.5400000000009</v>
       </c>
       <c r="N15" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O15" s="6">
-        <v>6632.7000000000007</v>
+        <v>6612.5400000000009</v>
       </c>
       <c r="P15" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q15" s="6">
-        <v>-66.545000000000002</v>
+        <v>-66.209000000000003</v>
       </c>
       <c r="R15" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S15" s="6">
-        <v>-66.545000000000002</v>
+        <v>-66.209000000000003</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -1180,49 +1183,49 @@
         <v>4334</v>
       </c>
       <c r="C16" s="16">
-        <v>6639.7333333333327</v>
+        <v>6621.3090909090888</v>
       </c>
       <c r="D16" s="16">
         <v>4314</v>
       </c>
       <c r="E16" s="16">
-        <v>6639.7333333333327</v>
+        <v>6621.3090909090888</v>
       </c>
       <c r="F16" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G16" s="12">
-        <v>-66.662222222222169</v>
+        <v>-66.355151515151505</v>
       </c>
       <c r="H16" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I16" s="12">
-        <v>-66.662222222222169</v>
+        <v>-66.355151515151505</v>
       </c>
       <c r="L16" s="6">
         <v>4330.12</v>
       </c>
       <c r="M16" s="6">
-        <v>6639.0000000000009</v>
+        <v>6613.8000000000011</v>
       </c>
       <c r="N16" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O16" s="6">
-        <v>6639.0000000000009</v>
+        <v>6613.8000000000011</v>
       </c>
       <c r="P16" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q16" s="6">
-        <v>-66.650000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="R16" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S16" s="6">
-        <v>-66.650000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -1236,50 +1239,50 @@
         <v>4334</v>
       </c>
       <c r="C17" s="16">
-        <v>6644.7999999999993</v>
+        <v>6622.6909090909066</v>
       </c>
       <c r="D17" s="16">
         <v>4314</v>
       </c>
       <c r="E17" s="16">
-        <v>6644.7999999999993</v>
+        <v>6622.6909090909066</v>
       </c>
       <c r="F17" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G17" s="12">
-        <v>-66.74666666666667</v>
+        <v>-66.378181818181829</v>
       </c>
       <c r="H17" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I17" s="12">
-        <v>-66.74666666666667</v>
+        <v>-66.378181818181829</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="6">
         <v>4330.12</v>
       </c>
       <c r="M17" s="6">
-        <v>6645.3000000000011</v>
+        <v>6615.0600000000013</v>
       </c>
       <c r="N17" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O17" s="6">
-        <v>6645.3000000000011</v>
+        <v>6615.0600000000013</v>
       </c>
       <c r="P17" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q17" s="6">
-        <v>-66.754999999999995</v>
+        <v>-66.251000000000005</v>
       </c>
       <c r="R17" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S17" s="6">
-        <v>-66.754999999999995</v>
+        <v>-66.251000000000005</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -1293,50 +1296,50 @@
         <v>4334</v>
       </c>
       <c r="C18" s="16">
-        <v>6649.8666666666659</v>
+        <v>6624.0727272727245</v>
       </c>
       <c r="D18" s="16">
         <v>4314</v>
       </c>
       <c r="E18" s="16">
-        <v>6649.8666666666659</v>
+        <v>6624.0727272727245</v>
       </c>
       <c r="F18" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G18" s="12">
-        <v>-66.83111111111117</v>
+        <v>-66.401212121211998</v>
       </c>
       <c r="H18" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I18" s="12">
-        <v>-66.83111111111117</v>
+        <v>-66.401212121211998</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6">
         <v>4330.12</v>
       </c>
       <c r="M18" s="6">
-        <v>6651.6000000000013</v>
+        <v>6616.3200000000015</v>
       </c>
       <c r="N18" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O18" s="6">
-        <v>6651.6000000000013</v>
+        <v>6616.3200000000015</v>
       </c>
       <c r="P18" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q18" s="6">
-        <v>-66.86</v>
+        <v>-66.272000000000006</v>
       </c>
       <c r="R18" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S18" s="6">
-        <v>-66.86</v>
+        <v>-66.272000000000006</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -1350,49 +1353,49 @@
         <v>4334</v>
       </c>
       <c r="C19" s="16">
-        <v>6654.9333333333325</v>
+        <v>6625.4545454545423</v>
       </c>
       <c r="D19" s="16">
         <v>4314</v>
       </c>
       <c r="E19" s="16">
-        <v>6654.9333333333325</v>
+        <v>6625.4545454545423</v>
       </c>
       <c r="F19" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G19" s="12">
-        <v>-66.9155555555555</v>
+        <v>-66.424242424242337</v>
       </c>
       <c r="H19" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I19" s="12">
-        <v>-66.9155555555555</v>
+        <v>-66.424242424242337</v>
       </c>
       <c r="L19" s="6">
         <v>4330.12</v>
       </c>
       <c r="M19" s="6">
-        <v>6657.9000000000015</v>
+        <v>6617.5800000000017</v>
       </c>
       <c r="N19" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O19" s="6">
-        <v>6657.9000000000015</v>
+        <v>6617.5800000000017</v>
       </c>
       <c r="P19" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q19" s="6">
-        <v>-66.965000000000003</v>
+        <v>-66.293000000000006</v>
       </c>
       <c r="R19" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S19" s="6">
-        <v>-66.965000000000003</v>
+        <v>-66.293000000000006</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -1406,49 +1409,49 @@
         <v>4334</v>
       </c>
       <c r="C20" s="16">
-        <v>6659.9999999999991</v>
+        <v>6626.8363636363601</v>
       </c>
       <c r="D20" s="16">
         <v>4314</v>
       </c>
       <c r="E20" s="16">
-        <v>6659.9999999999991</v>
+        <v>6626.8363636363601</v>
       </c>
       <c r="F20" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G20" s="12">
-        <v>-67</v>
+        <v>-66.447272727272662</v>
       </c>
       <c r="H20" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I20" s="12">
-        <v>-67</v>
+        <v>-66.447272727272662</v>
       </c>
       <c r="L20" s="6">
         <v>4330.12</v>
       </c>
       <c r="M20" s="6">
-        <v>6664.2000000000016</v>
+        <v>6618.840000000002</v>
       </c>
       <c r="N20" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O20" s="6">
-        <v>6664.2000000000016</v>
+        <v>6618.840000000002</v>
       </c>
       <c r="P20" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q20" s="6">
-        <v>-67.069999999999993</v>
+        <v>-66.313999999999993</v>
       </c>
       <c r="R20" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S20" s="6">
-        <v>-67.069999999999993</v>
+        <v>-66.313999999999993</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -1462,49 +1465,49 @@
         <v>4334</v>
       </c>
       <c r="C21" s="16">
-        <v>6665.0666666666657</v>
+        <v>6628.218181818178</v>
       </c>
       <c r="D21" s="16">
         <v>4314</v>
       </c>
       <c r="E21" s="16">
-        <v>6665.0666666666657</v>
+        <v>6628.218181818178</v>
       </c>
       <c r="F21" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G21" s="12">
-        <v>-67.0844444444445</v>
+        <v>-66.470303030303</v>
       </c>
       <c r="H21" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I21" s="12">
-        <v>-67.0844444444445</v>
+        <v>-66.470303030303</v>
       </c>
       <c r="L21" s="6">
         <v>4330.12</v>
       </c>
       <c r="M21" s="6">
-        <v>6670.5000000000018</v>
+        <v>6620.1000000000022</v>
       </c>
       <c r="N21" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O21" s="6">
-        <v>6670.5000000000018</v>
+        <v>6620.1000000000022</v>
       </c>
       <c r="P21" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q21" s="6">
-        <v>-67.174999999999997</v>
+        <v>-66.334999999999994</v>
       </c>
       <c r="R21" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S21" s="6">
-        <v>-67.174999999999997</v>
+        <v>-66.334999999999994</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -1518,49 +1521,49 @@
         <v>4334</v>
       </c>
       <c r="C22" s="16">
-        <v>6670.1333333333323</v>
+        <v>6629.5999999999958</v>
       </c>
       <c r="D22" s="16">
         <v>4314</v>
       </c>
       <c r="E22" s="16">
-        <v>6670.1333333333323</v>
+        <v>6629.5999999999958</v>
       </c>
       <c r="F22" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G22" s="12">
-        <v>-67.16888888888883</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="H22" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I22" s="12">
-        <v>-67.16888888888883</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="L22" s="6">
         <v>4330.12</v>
       </c>
       <c r="M22" s="6">
-        <v>6676.800000000002</v>
+        <v>6621.3600000000024</v>
       </c>
       <c r="N22" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O22" s="6">
-        <v>6676.800000000002</v>
+        <v>6621.3600000000024</v>
       </c>
       <c r="P22" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q22" s="6">
-        <v>-67.28</v>
+        <v>-66.355999999999995</v>
       </c>
       <c r="R22" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S22" s="6">
-        <v>-67.28</v>
+        <v>-66.355999999999995</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -1574,49 +1577,49 @@
         <v>4334</v>
       </c>
       <c r="C23" s="16">
-        <v>6675.1999999999989</v>
+        <v>6630.9818181818137</v>
       </c>
       <c r="D23" s="16">
         <v>4314</v>
       </c>
       <c r="E23" s="16">
-        <v>6675.1999999999989</v>
+        <v>6630.9818181818137</v>
       </c>
       <c r="F23" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G23" s="12">
-        <v>-67.25333333333333</v>
+        <v>-66.516363636363494</v>
       </c>
       <c r="H23" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I23" s="12">
-        <v>-67.25333333333333</v>
+        <v>-66.516363636363494</v>
       </c>
       <c r="L23" s="6">
         <v>4330.12</v>
       </c>
       <c r="M23" s="6">
-        <v>6683.1000000000022</v>
+        <v>6622.6200000000026</v>
       </c>
       <c r="N23" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O23" s="6">
-        <v>6683.1000000000022</v>
+        <v>6622.6200000000026</v>
       </c>
       <c r="P23" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q23" s="6">
-        <v>-67.385000000000005</v>
+        <v>-66.376999999999995</v>
       </c>
       <c r="R23" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S23" s="6">
-        <v>-67.385000000000005</v>
+        <v>-66.376999999999995</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -1630,49 +1633,49 @@
         <v>4334</v>
       </c>
       <c r="C24" s="16">
-        <v>6680.2666666666655</v>
+        <v>6632.3636363636315</v>
       </c>
       <c r="D24" s="16">
         <v>4314</v>
       </c>
       <c r="E24" s="16">
-        <v>6680.2666666666655</v>
+        <v>6632.3636363636315</v>
       </c>
       <c r="F24" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G24" s="12">
-        <v>-67.337777777777831</v>
+        <v>-66.539393939393833</v>
       </c>
       <c r="H24" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I24" s="12">
-        <v>-67.337777777777831</v>
+        <v>-66.539393939393833</v>
       </c>
       <c r="L24" s="6">
         <v>4330.12</v>
       </c>
       <c r="M24" s="6">
-        <v>6689.4000000000024</v>
+        <v>6623.8800000000028</v>
       </c>
       <c r="N24" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O24" s="6">
-        <v>6689.4000000000024</v>
+        <v>6623.8800000000028</v>
       </c>
       <c r="P24" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q24" s="6">
-        <v>-67.489999999999995</v>
+        <v>-66.397999999999996</v>
       </c>
       <c r="R24" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S24" s="6">
-        <v>-67.489999999999995</v>
+        <v>-66.397999999999996</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -1686,49 +1689,49 @@
         <v>4334</v>
       </c>
       <c r="C25" s="16">
-        <v>6685.3333333333321</v>
+        <v>6633.7454545454493</v>
       </c>
       <c r="D25" s="16">
         <v>4314</v>
       </c>
       <c r="E25" s="16">
-        <v>6685.3333333333321</v>
+        <v>6633.7454545454493</v>
       </c>
       <c r="F25" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G25" s="12">
-        <v>-67.42222222222216</v>
+        <v>-66.562424242424171</v>
       </c>
       <c r="H25" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I25" s="12">
-        <v>-67.42222222222216</v>
+        <v>-66.562424242424171</v>
       </c>
       <c r="L25" s="6">
         <v>4330.12</v>
       </c>
       <c r="M25" s="6">
-        <v>6695.7000000000025</v>
+        <v>6625.1400000000031</v>
       </c>
       <c r="N25" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O25" s="6">
-        <v>6695.7000000000025</v>
+        <v>6625.1400000000031</v>
       </c>
       <c r="P25" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q25" s="6">
-        <v>-67.594999999999999</v>
+        <v>-66.418999999999997</v>
       </c>
       <c r="R25" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S25" s="6">
-        <v>-67.594999999999999</v>
+        <v>-66.418999999999997</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -1742,49 +1745,49 @@
         <v>4334</v>
       </c>
       <c r="C26" s="16">
-        <v>6690.3999999999987</v>
+        <v>6635.1272727272672</v>
       </c>
       <c r="D26" s="16">
         <v>4314</v>
       </c>
       <c r="E26" s="16">
-        <v>6690.3999999999987</v>
+        <v>6635.1272727272672</v>
       </c>
       <c r="F26" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G26" s="12">
-        <v>-67.506666666666661</v>
+        <v>-66.585454545454496</v>
       </c>
       <c r="H26" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I26" s="12">
-        <v>-67.506666666666661</v>
+        <v>-66.585454545454496</v>
       </c>
       <c r="L26" s="6">
         <v>4330.12</v>
       </c>
       <c r="M26" s="6">
-        <v>6702.0000000000027</v>
+        <v>6626.4000000000033</v>
       </c>
       <c r="N26" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O26" s="6">
-        <v>6702.0000000000027</v>
+        <v>6626.4000000000033</v>
       </c>
       <c r="P26" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q26" s="6">
-        <v>-67.033333333333331</v>
+        <v>-66.44</v>
       </c>
       <c r="R26" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S26" s="6">
-        <v>-67.033333333333331</v>
+        <v>-66.44</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -1798,49 +1801,49 @@
         <v>4334</v>
       </c>
       <c r="C27" s="16">
-        <v>6695.4666666666653</v>
+        <v>6636.509090909085</v>
       </c>
       <c r="D27" s="16">
         <v>4314</v>
       </c>
       <c r="E27" s="16">
-        <v>6695.4666666666653</v>
+        <v>6636.509090909085</v>
       </c>
       <c r="F27" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G27" s="12">
-        <v>-67.591111111111161</v>
+        <v>-66.608484848484665</v>
       </c>
       <c r="H27" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I27" s="12">
-        <v>-67.591111111111161</v>
+        <v>-66.608484848484665</v>
       </c>
       <c r="L27" s="6">
         <v>4330.12</v>
       </c>
       <c r="M27" s="6">
-        <v>6708.3000000000029</v>
+        <v>6627.6600000000035</v>
       </c>
       <c r="N27" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O27" s="6">
-        <v>6708.3000000000029</v>
+        <v>6627.6600000000035</v>
       </c>
       <c r="P27" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q27" s="6">
-        <v>-67.138333333333335</v>
+        <v>-66.460999999999999</v>
       </c>
       <c r="R27" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S27" s="6">
-        <v>-67.138333333333335</v>
+        <v>-66.460999999999999</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -1854,49 +1857,49 @@
         <v>4334</v>
       </c>
       <c r="C28" s="16">
-        <v>6700.5333333333319</v>
+        <v>6637.8909090909028</v>
       </c>
       <c r="D28" s="16">
         <v>4314</v>
       </c>
       <c r="E28" s="16">
-        <v>6700.5333333333319</v>
+        <v>6637.8909090909028</v>
       </c>
       <c r="F28" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G28" s="12">
-        <v>-67.008888888888833</v>
+        <v>-66.631515151515003</v>
       </c>
       <c r="H28" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I28" s="12">
-        <v>-67.008888888888833</v>
+        <v>-66.631515151515003</v>
       </c>
       <c r="L28" s="6">
         <v>4330.12</v>
       </c>
       <c r="M28" s="6">
-        <v>6714.6000000000031</v>
+        <v>6628.9200000000037</v>
       </c>
       <c r="N28" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O28" s="6">
-        <v>6714.6000000000031</v>
+        <v>6628.9200000000037</v>
       </c>
       <c r="P28" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q28" s="6">
-        <v>-67.243333333333339</v>
+        <v>-66.481999999999999</v>
       </c>
       <c r="R28" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S28" s="6">
-        <v>-67.243333333333339</v>
+        <v>-66.481999999999999</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -1910,49 +1913,49 @@
         <v>4334</v>
       </c>
       <c r="C29" s="16">
-        <v>6705.5999999999985</v>
+        <v>6639.2727272727207</v>
       </c>
       <c r="D29" s="16">
         <v>4314</v>
       </c>
       <c r="E29" s="16">
-        <v>6705.5999999999985</v>
+        <v>6639.2727272727207</v>
       </c>
       <c r="F29" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G29" s="12">
-        <v>-67.093333333333334</v>
+        <v>-66.654545454545328</v>
       </c>
       <c r="H29" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I29" s="12">
-        <v>-67.093333333333334</v>
+        <v>-66.654545454545328</v>
       </c>
       <c r="L29" s="6">
         <v>4330.12</v>
       </c>
       <c r="M29" s="6">
-        <v>6720.9000000000033</v>
+        <v>6630.1800000000039</v>
       </c>
       <c r="N29" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O29" s="6">
-        <v>6720.9000000000033</v>
+        <v>6630.1800000000039</v>
       </c>
       <c r="P29" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q29" s="6">
-        <v>-67.348333333333329</v>
+        <v>-66.503</v>
       </c>
       <c r="R29" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S29" s="6">
-        <v>-67.348333333333329</v>
+        <v>-66.503</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -1966,49 +1969,49 @@
         <v>4334</v>
       </c>
       <c r="C30" s="16">
-        <v>6710.6666666666652</v>
+        <v>6640.6545454545385</v>
       </c>
       <c r="D30" s="16">
         <v>4314</v>
       </c>
       <c r="E30" s="16">
-        <v>6710.6666666666652</v>
+        <v>6640.6545454545385</v>
       </c>
       <c r="F30" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G30" s="12">
-        <v>-67.177777777777834</v>
+        <v>-66.677575757575667</v>
       </c>
       <c r="H30" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I30" s="12">
-        <v>-67.177777777777834</v>
+        <v>-66.677575757575667</v>
       </c>
       <c r="L30" s="6">
         <v>4330.12</v>
       </c>
       <c r="M30" s="6">
-        <v>6727.2000000000035</v>
+        <v>6631.4400000000041</v>
       </c>
       <c r="N30" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O30" s="6">
-        <v>6727.2000000000035</v>
+        <v>6631.4400000000041</v>
       </c>
       <c r="P30" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q30" s="6">
-        <v>-67.453333333333333</v>
+        <v>-66.524000000000001</v>
       </c>
       <c r="R30" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S30" s="6">
-        <v>-67.453333333333333</v>
+        <v>-66.524000000000001</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -2022,49 +2025,49 @@
         <v>4334</v>
       </c>
       <c r="C31" s="16">
-        <v>6715.7333333333318</v>
+        <v>6642.0363636363563</v>
       </c>
       <c r="D31" s="16">
         <v>4314</v>
       </c>
       <c r="E31" s="16">
-        <v>6715.7333333333318</v>
+        <v>6642.0363636363563</v>
       </c>
       <c r="F31" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G31" s="12">
-        <v>-67.262222222222164</v>
+        <v>-66.700606060606006</v>
       </c>
       <c r="H31" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I31" s="12">
-        <v>-67.262222222222164</v>
+        <v>-66.700606060606006</v>
       </c>
       <c r="L31" s="6">
         <v>4330.12</v>
       </c>
       <c r="M31" s="6">
-        <v>6733.5000000000036</v>
+        <v>6632.7000000000044</v>
       </c>
       <c r="N31" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O31" s="6">
-        <v>6733.5000000000036</v>
+        <v>6632.7000000000044</v>
       </c>
       <c r="P31" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q31" s="6">
-        <v>-67.558333333333337</v>
+        <v>-66.545000000000002</v>
       </c>
       <c r="R31" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S31" s="6">
-        <v>-67.558333333333337</v>
+        <v>-66.545000000000002</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -2078,49 +2081,49 @@
         <v>4334</v>
       </c>
       <c r="C32" s="16">
-        <v>6720.7999999999984</v>
+        <v>6643.4181818181742</v>
       </c>
       <c r="D32" s="16">
         <v>4314</v>
       </c>
       <c r="E32" s="16">
-        <v>6720.7999999999984</v>
+        <v>6643.4181818181742</v>
       </c>
       <c r="F32" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G32" s="12">
-        <v>-67.346666666666664</v>
+        <v>-66.72363636363616</v>
       </c>
       <c r="H32" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I32" s="12">
-        <v>-67.346666666666664</v>
+        <v>-66.72363636363616</v>
       </c>
       <c r="L32" s="6">
         <v>4330.12</v>
       </c>
       <c r="M32" s="6">
-        <v>6739.8000000000038</v>
+        <v>6633.9600000000046</v>
       </c>
       <c r="N32" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O32" s="6">
-        <v>6739.8000000000038</v>
+        <v>6633.9600000000046</v>
       </c>
       <c r="P32" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q32" s="6">
-        <v>-67.663333333333327</v>
+        <v>-66.566000000000003</v>
       </c>
       <c r="R32" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S32" s="6">
-        <v>-67.663333333333327</v>
+        <v>-66.566000000000003</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -2134,49 +2137,49 @@
         <v>4334</v>
       </c>
       <c r="C33" s="16">
-        <v>6725.866666666665</v>
+        <v>6644.799999999992</v>
       </c>
       <c r="D33" s="16">
         <v>4314</v>
       </c>
       <c r="E33" s="16">
-        <v>6725.866666666665</v>
+        <v>6644.799999999992</v>
       </c>
       <c r="F33" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G33" s="12">
-        <v>-67.431111111110994</v>
+        <v>-66.746666666666499</v>
       </c>
       <c r="H33" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I33" s="12">
-        <v>-67.431111111110994</v>
+        <v>-66.746666666666499</v>
       </c>
       <c r="L33" s="6">
         <v>4330.12</v>
       </c>
       <c r="M33" s="6">
-        <v>6746.100000000004</v>
+        <v>6635.2200000000048</v>
       </c>
       <c r="N33" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O33" s="6">
-        <v>6746.100000000004</v>
+        <v>6635.2200000000048</v>
       </c>
       <c r="P33" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q33" s="6">
-        <v>-67.768333333333331</v>
+        <v>-66.587000000000003</v>
       </c>
       <c r="R33" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S33" s="6">
-        <v>-67.768333333333331</v>
+        <v>-66.587000000000003</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -2190,49 +2193,49 @@
         <v>4334</v>
       </c>
       <c r="C34" s="16">
-        <v>6730.9333333333316</v>
+        <v>6646.1818181818098</v>
       </c>
       <c r="D34" s="16">
         <v>4314</v>
       </c>
       <c r="E34" s="16">
-        <v>6730.9333333333316</v>
+        <v>6646.1818181818098</v>
       </c>
       <c r="F34" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G34" s="12">
-        <v>-67.515555555555494</v>
+        <v>-66.769696969696838</v>
       </c>
       <c r="H34" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I34" s="12">
-        <v>-67.515555555555494</v>
+        <v>-66.769696969696838</v>
       </c>
       <c r="L34" s="6">
         <v>4330.12</v>
       </c>
       <c r="M34" s="6">
-        <v>6752.4000000000042</v>
+        <v>6636.480000000005</v>
       </c>
       <c r="N34" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O34" s="6">
-        <v>6752.4000000000042</v>
+        <v>6636.480000000005</v>
       </c>
       <c r="P34" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q34" s="6">
-        <v>-67.873333333333335</v>
+        <v>-66.60800000000016</v>
       </c>
       <c r="R34" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S34" s="6">
-        <v>-67.873333333333335</v>
+        <v>-66.60800000000016</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -3258,13 +3261,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C2" s="12">
-        <v>-66.493333333333339</v>
+        <v>-66.239999999999995</v>
       </c>
       <c r="D2" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E2" s="12">
-        <v>-66.493333333333339</v>
+        <v>-66.239999999999995</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3275,13 +3278,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C3" s="12">
-        <v>-66.465185185185163</v>
+        <v>-66.268148148148171</v>
       </c>
       <c r="D3" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E3" s="12">
-        <v>-66.465185185185163</v>
+        <v>-66.268148148148171</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3292,13 +3295,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C4" s="12">
-        <v>-66.437037037037001</v>
+        <v>-66.296296296296333</v>
       </c>
       <c r="D4" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E4" s="12">
-        <v>-66.437037037037001</v>
+        <v>-66.296296296296333</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3309,13 +3312,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C5" s="12">
-        <v>-66.408888888888839</v>
+        <v>-66.324444444444495</v>
       </c>
       <c r="D5" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E5" s="12">
-        <v>-66.408888888888839</v>
+        <v>-66.324444444444495</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3326,13 +3329,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C6" s="12">
-        <v>-66.380740740740663</v>
+        <v>-66.352592592592671</v>
       </c>
       <c r="D6" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E6" s="12">
-        <v>-66.380740740740663</v>
+        <v>-66.352592592592671</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3343,13 +3346,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C7" s="12">
-        <v>-66.352592592592671</v>
+        <v>-66.380740740740663</v>
       </c>
       <c r="D7" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E7" s="12">
-        <v>-66.352592592592671</v>
+        <v>-66.380740740740663</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3360,13 +3363,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C8" s="12">
-        <v>-66.324444444444495</v>
+        <v>-66.408888888888839</v>
       </c>
       <c r="D8" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E8" s="12">
-        <v>-66.324444444444495</v>
+        <v>-66.408888888888839</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3377,13 +3380,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C9" s="12">
-        <v>-66.296296296296333</v>
+        <v>-66.437037037037001</v>
       </c>
       <c r="D9" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E9" s="12">
-        <v>-66.296296296296333</v>
+        <v>-66.437037037037001</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3394,13 +3397,13 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C10" s="12">
-        <v>-66.268148148148171</v>
+        <v>-66.465185185185163</v>
       </c>
       <c r="D10" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E10" s="12">
-        <v>-66.268148148148171</v>
+        <v>-66.465185185185163</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -3411,184 +3414,164 @@
         <v>43.56666666666667</v>
       </c>
       <c r="C11" s="12">
-        <v>-66.239999999999995</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="D11" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="E11" s="12">
-        <v>-66.239999999999995</v>
+        <v>-66.493333333333339</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
-        <v>39</v>
+      <c r="A12" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="B12" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C12" s="6">
-        <v>-66.23</v>
+        <v>-66.125</v>
       </c>
       <c r="D12" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E12" s="6">
-        <v>-66.23</v>
+        <v>-66.125</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="19" t="s">
-        <v>40</v>
+      <c r="A13" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B13" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C13" s="6">
-        <v>-66.218333333333334</v>
+        <v>-66.16</v>
       </c>
       <c r="D13" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E13" s="6">
-        <v>-66.218333333333334</v>
+        <v>-66.16</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="19" t="s">
-        <v>41</v>
+      <c r="A14" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="B14" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C14" s="6">
-        <v>-66.206666666666663</v>
+        <v>-66.194999999999993</v>
       </c>
       <c r="D14" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E14" s="6">
-        <v>-66.206666666666663</v>
+        <v>-66.194999999999993</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
-        <v>42</v>
+      <c r="A15" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B15" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C15" s="6">
-        <v>-66.194999999999993</v>
+        <v>-66.23</v>
       </c>
       <c r="D15" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E15" s="6">
-        <v>-66.194999999999993</v>
+        <v>-66.23</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="19" t="s">
-        <v>43</v>
+      <c r="A16" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="B16" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C16" s="6">
-        <v>-66.183333333333337</v>
+        <v>-66.265000000000001</v>
       </c>
       <c r="D16" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E16" s="6">
-        <v>-66.183333333333337</v>
+        <v>-66.265000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>39</v>
+      <c r="A17" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B17" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C17" s="6">
-        <v>-66.171666666666667</v>
+        <v>-66.3</v>
       </c>
       <c r="D17" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E17" s="6">
-        <v>-66.171666666666667</v>
+        <v>-66.3</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
-        <v>40</v>
+      <c r="A18" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="B18" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C18" s="6">
-        <v>-66.16</v>
+        <v>-66.334999999999994</v>
       </c>
       <c r="D18" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E18" s="6">
-        <v>-66.16</v>
+        <v>-66.334999999999994</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="19" t="s">
-        <v>41</v>
+      <c r="A19" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B19" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="C19" s="6">
-        <v>-66.148333333333326</v>
+        <v>-66.37</v>
       </c>
       <c r="D19" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="E19" s="6">
-        <v>-66.148333333333326</v>
+        <v>-66.37</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6">
-        <v>43.502000000000002</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-66.13666666666667</v>
-      </c>
-      <c r="D20" s="6">
-        <v>43.247500000000002</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-66.13666666666667</v>
-      </c>
+      <c r="A20" s="19"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="6">
-        <v>43.502000000000002</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-66.125</v>
-      </c>
-      <c r="D21" s="6">
-        <v>43.247500000000002</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-66.125</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4612,13 +4595,13 @@
         <v>4334</v>
       </c>
       <c r="C2" s="16">
-        <v>6629.5999999999958</v>
+        <v>6614.4</v>
       </c>
       <c r="D2" s="16">
         <v>4314</v>
       </c>
       <c r="E2" s="16">
-        <v>6629.5999999999958</v>
+        <v>6614.4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -4629,13 +4612,13 @@
         <v>4334</v>
       </c>
       <c r="C3" s="16">
-        <v>6628.218181818178</v>
+        <v>6616.0888888888885</v>
       </c>
       <c r="D3" s="16">
         <v>4314</v>
       </c>
       <c r="E3" s="16">
-        <v>6628.218181818178</v>
+        <v>6616.0888888888885</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -4646,13 +4629,13 @@
         <v>4334</v>
       </c>
       <c r="C4" s="16">
-        <v>6626.8363636363601</v>
+        <v>6617.7777777777774</v>
       </c>
       <c r="D4" s="16">
         <v>4314</v>
       </c>
       <c r="E4" s="16">
-        <v>6626.8363636363601</v>
+        <v>6617.7777777777774</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -4663,13 +4646,13 @@
         <v>4334</v>
       </c>
       <c r="C5" s="16">
-        <v>6625.4545454545423</v>
+        <v>6619.4666666666662</v>
       </c>
       <c r="D5" s="16">
         <v>4314</v>
       </c>
       <c r="E5" s="16">
-        <v>6625.4545454545423</v>
+        <v>6619.4666666666662</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
@@ -4680,234 +4663,234 @@
         <v>4334</v>
       </c>
       <c r="C6" s="16">
-        <v>6624.0727272727245</v>
+        <v>6621.1555555555551</v>
       </c>
       <c r="D6" s="16">
         <v>4314</v>
       </c>
       <c r="E6" s="16">
-        <v>6624.0727272727245</v>
+        <v>6621.1555555555551</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
-        <v>44</v>
+      <c r="A7" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="B7" s="16">
         <v>4334</v>
       </c>
       <c r="C7" s="16">
-        <v>6622.6909090909066</v>
+        <v>6622.844444444444</v>
       </c>
       <c r="D7" s="16">
         <v>4314</v>
       </c>
       <c r="E7" s="16">
-        <v>6622.6909090909066</v>
+        <v>6622.844444444444</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="16">
         <v>4334</v>
       </c>
       <c r="C8" s="16">
-        <v>6621.3090909090888</v>
+        <v>6624.5333333333328</v>
       </c>
       <c r="D8" s="16">
         <v>4314</v>
       </c>
       <c r="E8" s="16">
-        <v>6621.3090909090888</v>
+        <v>6624.5333333333328</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="16">
         <v>4334</v>
       </c>
       <c r="C9" s="16">
-        <v>6619.927272727271</v>
+        <v>6626.2222222222217</v>
       </c>
       <c r="D9" s="16">
         <v>4314</v>
       </c>
       <c r="E9" s="16">
-        <v>6619.927272727271</v>
+        <v>6626.2222222222217</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="16">
         <v>4334</v>
       </c>
       <c r="C10" s="16">
-        <v>6618.5454545454531</v>
+        <v>6627.9111111111106</v>
       </c>
       <c r="D10" s="16">
         <v>4314</v>
       </c>
       <c r="E10" s="16">
-        <v>6618.5454545454531</v>
+        <v>6627.9111111111106</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="16">
         <v>4334</v>
       </c>
       <c r="C11" s="16">
-        <v>6617.1636363636353</v>
+        <v>6629.5999999999995</v>
       </c>
       <c r="D11" s="16">
         <v>4314</v>
       </c>
       <c r="E11" s="16">
-        <v>6617.1636363636353</v>
+        <v>6629.5999999999995</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="16">
-        <v>4334</v>
-      </c>
-      <c r="C12" s="16">
-        <v>6615.7818181818175</v>
-      </c>
-      <c r="D12" s="16">
-        <v>4314</v>
-      </c>
-      <c r="E12" s="16">
-        <v>6615.7818181818175</v>
+      <c r="A12" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="6">
+        <v>4330.12</v>
+      </c>
+      <c r="C12" s="6">
+        <v>6607.5</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4314.8500000000004</v>
+      </c>
+      <c r="E12" s="6">
+        <v>6607.5</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="6">
+        <v>4330.12</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6609.6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4314.8500000000004</v>
+      </c>
+      <c r="E13" s="6">
+        <v>6609.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="20" t="s">
         <v>44</v>
-      </c>
-      <c r="B13" s="16">
-        <v>4334</v>
-      </c>
-      <c r="C13" s="16">
-        <v>6614.4</v>
-      </c>
-      <c r="D13" s="16">
-        <v>4314</v>
-      </c>
-      <c r="E13" s="16">
-        <v>6614.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="19" t="s">
-        <v>39</v>
       </c>
       <c r="B14" s="6">
         <v>4330.12</v>
       </c>
       <c r="C14" s="6">
-        <v>6613.8000000000011</v>
+        <v>6611.7000000000007</v>
       </c>
       <c r="D14" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="E14" s="6">
-        <v>6613.8000000000011</v>
+        <v>6611.7000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
-        <v>40</v>
+      <c r="A15" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B15" s="6">
         <v>4330.12</v>
       </c>
       <c r="C15" s="6">
-        <v>6612.5400000000009</v>
+        <v>6613.8000000000011</v>
       </c>
       <c r="D15" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="E15" s="6">
-        <v>6612.5400000000009</v>
+        <v>6613.8000000000011</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16">
+      <c r="A16" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6">
         <v>4330.12</v>
       </c>
-      <c r="C16">
-        <v>6611.2800000000007</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="6">
+        <v>6615.9000000000015</v>
+      </c>
+      <c r="D16" s="6">
         <v>4314.8500000000004</v>
       </c>
-      <c r="E16">
-        <v>6611.2800000000007</v>
+      <c r="E16" s="6">
+        <v>6615.9000000000015</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17">
+      <c r="A17" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="6">
         <v>4330.12</v>
       </c>
-      <c r="C17">
-        <v>6610.02</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="6">
+        <v>6618.0000000000018</v>
+      </c>
+      <c r="D17" s="6">
         <v>4314.8500000000004</v>
       </c>
-      <c r="E17">
-        <v>6610.02</v>
+      <c r="E17" s="6">
+        <v>6618.0000000000018</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18">
+      <c r="A18" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="6">
         <v>4330.12</v>
       </c>
-      <c r="C18">
-        <v>6608.76</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="6">
+        <v>6620.1000000000022</v>
+      </c>
+      <c r="D18" s="6">
         <v>4314.8500000000004</v>
       </c>
-      <c r="E18">
-        <v>6608.76</v>
+      <c r="E18" s="6">
+        <v>6620.1000000000022</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19">
+        <v>46</v>
+      </c>
+      <c r="B19" s="6">
         <v>4330.12</v>
       </c>
-      <c r="C19">
-        <v>6607.5</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="6">
+        <v>6622.2000000000025</v>
+      </c>
+      <c r="D19" s="6">
         <v>4314.8500000000004</v>
       </c>
-      <c r="E19">
-        <v>6607.5</v>
+      <c r="E19" s="6">
+        <v>6622.2000000000025</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -6014,11 +5997,11 @@
       </c>
       <c r="V3" s="8">
         <f>B4</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X3" s="6">
         <f t="shared" ref="X3:X4" si="8">V3</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE3" s="6" t="s">
         <v>23</v>
@@ -6045,7 +6028,7 @@
       </c>
       <c r="B4" s="8">
         <f>'Data Entry'!B1</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -6060,7 +6043,7 @@
       </c>
       <c r="L4" s="8">
         <f>B4</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -6072,15 +6055,15 @@
       </c>
       <c r="V4" s="6">
         <f>V3*2</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="X4" s="6">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Y4" s="6">
         <f>X4</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>24</v>
@@ -6108,7 +6091,7 @@
       </c>
       <c r="B5" s="6">
         <f>B4*2</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -6120,7 +6103,7 @@
       </c>
       <c r="L5" s="6">
         <f>(L31-L3)/(L4-1)</f>
-        <v>6.3000000000001819</v>
+        <v>1.2600000000000364</v>
       </c>
       <c r="P5" s="8" t="s">
         <v>26</v>
@@ -6130,15 +6113,15 @@
       </c>
       <c r="V5" s="6">
         <f>(V2-V25)/(V4-1)</f>
-        <v>2.6060000000000705</v>
+        <v>0.71072727272729186</v>
       </c>
       <c r="X5" s="6">
         <f t="shared" ref="X5:Y5" si="10">(X2-X25)/(X4-1)</f>
-        <v>1.9089999999999538</v>
+        <v>0.52063636363635102</v>
       </c>
       <c r="Y5" s="6">
         <f t="shared" si="10"/>
-        <v>2.8786666666668075</v>
+        <v>0.78509090909094748</v>
       </c>
       <c r="Z5" s="8" t="s">
         <v>26</v>
@@ -6168,7 +6151,7 @@
       </c>
       <c r="B6" s="6">
         <f>(B32-B3)/(B5-1)</f>
-        <v>5.0666666666669089</v>
+        <v>1.381818181818248</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>26</v>
@@ -6374,14 +6357,14 @@
       </c>
       <c r="M8" s="6">
         <f>M7+L5</f>
-        <v>6613.8</v>
+        <v>6608.76</v>
       </c>
       <c r="N8" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O8" s="6">
         <f t="shared" si="12"/>
-        <v>6613.8</v>
+        <v>6608.76</v>
       </c>
       <c r="P8" s="6">
         <f t="shared" si="13"/>
@@ -6389,7 +6372,7 @@
       </c>
       <c r="Q8" s="6">
         <f t="shared" si="14"/>
-        <v>-66.23</v>
+        <v>-66.146000000000001</v>
       </c>
       <c r="R8" s="6">
         <f t="shared" ref="R8:R30" si="29">(LEFT(N8,2)+((RIGHT(N8,LEN(N8)-2))/60))</f>
@@ -6397,7 +6380,7 @@
       </c>
       <c r="S8" s="6">
         <f t="shared" ref="S8" si="30">Q8</f>
-        <v>-66.23</v>
+        <v>-66.146000000000001</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" ref="U8:U24" si="31">U7+1</f>
@@ -6405,22 +6388,22 @@
       </c>
       <c r="V8" s="6">
         <f>V7+$V5</f>
-        <v>4504.7879999999996</v>
+        <v>4502.8927272727269</v>
       </c>
       <c r="W8" s="6">
         <v>6514</v>
       </c>
       <c r="X8" s="6">
         <f t="shared" ref="X8:Y8" si="32">X7+X5</f>
-        <v>4514.8819999999996</v>
+        <v>4513.4936363636361</v>
       </c>
       <c r="Y8" s="6">
         <f t="shared" si="32"/>
-        <v>6443.7426666666661</v>
+        <v>6441.6490909090908</v>
       </c>
       <c r="Z8" s="6">
         <f t="shared" si="16"/>
-        <v>45.079799999999999</v>
+        <v>45.048212121212167</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="17"/>
@@ -6428,11 +6411,11 @@
       </c>
       <c r="AB8" s="6">
         <f t="shared" si="18"/>
-        <v>45.248033333333332</v>
+        <v>45.224893939394001</v>
       </c>
       <c r="AC8" s="6">
         <f t="shared" si="19"/>
-        <v>-64.729044444444497</v>
+        <v>-64.694151515151503</v>
       </c>
       <c r="AE8" s="6">
         <v>2</v>
@@ -6479,14 +6462,14 @@
       </c>
       <c r="C9" s="6">
         <f>C8+B6</f>
-        <v>6619.4666666666662</v>
+        <v>6615.7818181818175</v>
       </c>
       <c r="D9" s="6">
         <v>4314</v>
       </c>
       <c r="E9" s="6">
         <f t="shared" si="24"/>
-        <v>6619.4666666666662</v>
+        <v>6615.7818181818175</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="25"/>
@@ -6494,7 +6477,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="26"/>
-        <v>-66.324444444444495</v>
+        <v>-66.263030303030334</v>
       </c>
       <c r="H9" s="6">
         <f t="shared" ref="H9:H31" si="35">(LEFT(D9,2)+((RIGHT(D9,LEN(D9)-2))/60))</f>
@@ -6502,7 +6485,7 @@
       </c>
       <c r="I9" s="6">
         <f t="shared" ref="I9" si="36">G9</f>
-        <v>-66.324444444444495</v>
+        <v>-66.263030303030334</v>
       </c>
       <c r="K9" s="6">
         <f t="shared" si="28"/>
@@ -6513,14 +6496,14 @@
       </c>
       <c r="M9" s="6">
         <f>M8+L5</f>
-        <v>6620.1</v>
+        <v>6610.02</v>
       </c>
       <c r="N9" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O9" s="6">
         <f t="shared" si="12"/>
-        <v>6620.1</v>
+        <v>6610.02</v>
       </c>
       <c r="P9" s="6">
         <f t="shared" si="13"/>
@@ -6528,7 +6511,7 @@
       </c>
       <c r="Q9" s="6">
         <f t="shared" si="14"/>
-        <v>-66.334999999999994</v>
+        <v>-66.167000000000002</v>
       </c>
       <c r="R9" s="6">
         <f t="shared" si="29"/>
@@ -6536,7 +6519,7 @@
       </c>
       <c r="S9" s="6">
         <f t="shared" ref="S9" si="37">Q9</f>
-        <v>-66.334999999999994</v>
+        <v>-66.167000000000002</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="31"/>
@@ -6544,22 +6527,22 @@
       </c>
       <c r="V9" s="6">
         <f>V8+$V5</f>
-        <v>4507.3939999999993</v>
+        <v>4503.603454545454</v>
       </c>
       <c r="W9" s="6">
         <v>6514</v>
       </c>
       <c r="X9" s="6">
         <f t="shared" ref="X9:Y9" si="38">X8+X5</f>
-        <v>4516.7909999999993</v>
+        <v>4514.0142727272723</v>
       </c>
       <c r="Y9" s="6">
         <f t="shared" si="38"/>
-        <v>6446.6213333333326</v>
+        <v>6442.434181818182</v>
       </c>
       <c r="Z9" s="6">
         <f t="shared" si="16"/>
-        <v>45.123233333333332</v>
+        <v>45.060057575757497</v>
       </c>
       <c r="AA9" s="6">
         <f t="shared" si="17"/>
@@ -6567,11 +6550,11 @@
       </c>
       <c r="AB9" s="6">
         <f t="shared" si="18"/>
-        <v>45.279850000000003</v>
+        <v>45.23357121212117</v>
       </c>
       <c r="AC9" s="6">
         <f t="shared" si="19"/>
-        <v>-64.777022222222172</v>
+        <v>-64.707236363636326</v>
       </c>
       <c r="AE9" s="6">
         <v>3</v>
@@ -6618,14 +6601,14 @@
       </c>
       <c r="C10" s="6">
         <f>C9+B6</f>
-        <v>6624.5333333333328</v>
+        <v>6617.1636363636353</v>
       </c>
       <c r="D10" s="6">
         <v>4314</v>
       </c>
       <c r="E10" s="6">
         <f t="shared" si="24"/>
-        <v>6624.5333333333328</v>
+        <v>6617.1636363636353</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="25"/>
@@ -6633,7 +6616,7 @@
       </c>
       <c r="G10" s="6">
         <f t="shared" si="26"/>
-        <v>-66.408888888888839</v>
+        <v>-66.286060606060673</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="35"/>
@@ -6641,7 +6624,7 @@
       </c>
       <c r="I10" s="6">
         <f t="shared" ref="I10" si="40">G10</f>
-        <v>-66.408888888888839</v>
+        <v>-66.286060606060673</v>
       </c>
       <c r="K10" s="6">
         <f t="shared" si="28"/>
@@ -6652,14 +6635,14 @@
       </c>
       <c r="M10" s="6">
         <f>M9+L5</f>
-        <v>6626.4000000000005</v>
+        <v>6611.2800000000007</v>
       </c>
       <c r="N10" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O10" s="6">
         <f t="shared" si="12"/>
-        <v>6626.4000000000005</v>
+        <v>6611.2800000000007</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="13"/>
@@ -6667,7 +6650,7 @@
       </c>
       <c r="Q10" s="6">
         <f t="shared" si="14"/>
-        <v>-66.44</v>
+        <v>-66.188000000000002</v>
       </c>
       <c r="R10" s="6">
         <f t="shared" si="29"/>
@@ -6675,7 +6658,7 @@
       </c>
       <c r="S10" s="6">
         <f t="shared" ref="S10" si="41">Q10</f>
-        <v>-66.44</v>
+        <v>-66.188000000000002</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="31"/>
@@ -6683,22 +6666,22 @@
       </c>
       <c r="V10" s="6">
         <f>V9+$V5</f>
-        <v>4509.9999999999991</v>
+        <v>4504.3141818181812</v>
       </c>
       <c r="W10" s="6">
         <v>6514</v>
       </c>
       <c r="X10" s="6">
         <f t="shared" ref="X10:Y10" si="42">X9+X5</f>
-        <v>4518.6999999999989</v>
+        <v>4514.5349090909085</v>
       </c>
       <c r="Y10" s="6">
         <f t="shared" si="42"/>
-        <v>6449.4999999999991</v>
+        <v>6443.2192727272732</v>
       </c>
       <c r="Z10" s="6">
         <f t="shared" si="16"/>
-        <v>45.166666666666664</v>
+        <v>45.071903030302998</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="17"/>
@@ -6706,11 +6689,11 @@
       </c>
       <c r="AB10" s="6">
         <f t="shared" si="18"/>
-        <v>45.311666666666667</v>
+        <v>45.242248484848503</v>
       </c>
       <c r="AC10" s="6">
         <f t="shared" si="19"/>
-        <v>-64.825000000000003</v>
+        <v>-64.720321212121164</v>
       </c>
       <c r="AE10" s="6">
         <v>4</v>
@@ -6757,14 +6740,14 @@
       </c>
       <c r="C11" s="6">
         <f>C10+B6</f>
-        <v>6629.5999999999995</v>
+        <v>6618.5454545454531</v>
       </c>
       <c r="D11" s="6">
         <v>4314</v>
       </c>
       <c r="E11" s="6">
         <f t="shared" si="24"/>
-        <v>6629.5999999999995</v>
+        <v>6618.5454545454531</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="25"/>
@@ -6772,7 +6755,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="26"/>
-        <v>-66.493333333333339</v>
+        <v>-66.309090909090827</v>
       </c>
       <c r="H11" s="6">
         <f t="shared" si="35"/>
@@ -6780,7 +6763,7 @@
       </c>
       <c r="I11" s="6">
         <f t="shared" ref="I11" si="44">G11</f>
-        <v>-66.493333333333339</v>
+        <v>-66.309090909090827</v>
       </c>
       <c r="K11" s="6">
         <f t="shared" si="28"/>
@@ -6791,14 +6774,14 @@
       </c>
       <c r="M11" s="6">
         <f>M10+L5</f>
-        <v>6632.7000000000007</v>
+        <v>6612.5400000000009</v>
       </c>
       <c r="N11" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O11" s="6">
         <f t="shared" si="12"/>
-        <v>6632.7000000000007</v>
+        <v>6612.5400000000009</v>
       </c>
       <c r="P11" s="6">
         <f t="shared" si="13"/>
@@ -6806,7 +6789,7 @@
       </c>
       <c r="Q11" s="6">
         <f t="shared" si="14"/>
-        <v>-66.545000000000002</v>
+        <v>-66.209000000000003</v>
       </c>
       <c r="R11" s="6">
         <f t="shared" si="29"/>
@@ -6814,7 +6797,7 @@
       </c>
       <c r="S11" s="6">
         <f t="shared" ref="S11" si="45">Q11</f>
-        <v>-66.545000000000002</v>
+        <v>-66.209000000000003</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="31"/>
@@ -6822,22 +6805,22 @@
       </c>
       <c r="V11" s="6">
         <f>V10+$V5</f>
-        <v>4512.6059999999989</v>
+        <v>4505.0249090909083</v>
       </c>
       <c r="W11" s="6">
         <v>6514</v>
       </c>
       <c r="X11" s="6">
         <f t="shared" ref="X11:Y11" si="46">X10+X5</f>
-        <v>4520.6089999999986</v>
+        <v>4515.0555454545447</v>
       </c>
       <c r="Y11" s="6">
         <f t="shared" si="46"/>
-        <v>6452.3786666666656</v>
+        <v>6444.0043636363644</v>
       </c>
       <c r="Z11" s="6">
         <f t="shared" si="16"/>
-        <v>45.210099999999997</v>
+        <v>45.083748484848499</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="17"/>
@@ -6845,11 +6828,11 @@
       </c>
       <c r="AB11" s="6">
         <f t="shared" si="18"/>
-        <v>45.343483333333332</v>
+        <v>45.250925757575665</v>
       </c>
       <c r="AC11" s="6">
         <f t="shared" si="19"/>
-        <v>-64.872977777777834</v>
+        <v>-64.733406060606001</v>
       </c>
       <c r="AE11" s="6" t="s">
         <v>28</v>
@@ -6893,14 +6876,14 @@
       </c>
       <c r="C12" s="6">
         <f>C11+B6</f>
-        <v>6634.6666666666661</v>
+        <v>6619.927272727271</v>
       </c>
       <c r="D12" s="6">
         <v>4314</v>
       </c>
       <c r="E12" s="6">
         <f t="shared" si="24"/>
-        <v>6634.6666666666661</v>
+        <v>6619.927272727271</v>
       </c>
       <c r="F12" s="6">
         <f t="shared" si="25"/>
@@ -6908,7 +6891,7 @@
       </c>
       <c r="G12" s="6">
         <f t="shared" si="26"/>
-        <v>-66.57777777777784</v>
+        <v>-66.332121212121166</v>
       </c>
       <c r="H12" s="6">
         <f t="shared" si="35"/>
@@ -6916,7 +6899,7 @@
       </c>
       <c r="I12" s="6">
         <f t="shared" ref="I12" si="51">G12</f>
-        <v>-66.57777777777784</v>
+        <v>-66.332121212121166</v>
       </c>
       <c r="K12" s="6">
         <f t="shared" si="28"/>
@@ -6927,14 +6910,14 @@
       </c>
       <c r="M12" s="6">
         <f>M11+L5</f>
-        <v>6639.0000000000009</v>
+        <v>6613.8000000000011</v>
       </c>
       <c r="N12" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O12" s="6">
         <f t="shared" si="12"/>
-        <v>6639.0000000000009</v>
+        <v>6613.8000000000011</v>
       </c>
       <c r="P12" s="6">
         <f t="shared" si="13"/>
@@ -6942,7 +6925,7 @@
       </c>
       <c r="Q12" s="6">
         <f t="shared" si="14"/>
-        <v>-66.650000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="R12" s="6">
         <f t="shared" si="29"/>
@@ -6950,7 +6933,7 @@
       </c>
       <c r="S12" s="6">
         <f t="shared" ref="S12" si="52">Q12</f>
-        <v>-66.650000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="31"/>
@@ -6958,22 +6941,22 @@
       </c>
       <c r="V12" s="6">
         <f>V11+$V5</f>
-        <v>4515.2119999999986</v>
+        <v>4505.7356363636354</v>
       </c>
       <c r="W12" s="6">
         <v>6514</v>
       </c>
       <c r="X12" s="6">
         <f t="shared" ref="X12:Y12" si="53">X11+X5</f>
-        <v>4522.5179999999982</v>
+        <v>4515.5761818181809</v>
       </c>
       <c r="Y12" s="6">
         <f t="shared" si="53"/>
-        <v>6455.2573333333321</v>
+        <v>6444.7894545454556</v>
       </c>
       <c r="Z12" s="6">
         <f t="shared" si="16"/>
-        <v>45.25353333333333</v>
+        <v>45.095593939394</v>
       </c>
       <c r="AA12" s="6">
         <f t="shared" si="17"/>
@@ -6981,11 +6964,11 @@
       </c>
       <c r="AB12" s="6">
         <f t="shared" si="18"/>
-        <v>45.375300000000003</v>
+        <v>45.259603030302998</v>
       </c>
       <c r="AC12" s="6">
         <f t="shared" si="19"/>
-        <v>-64.920955555555494</v>
+        <v>-64.746490909090994</v>
       </c>
     </row>
     <row r="13" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
@@ -6998,14 +6981,14 @@
       </c>
       <c r="C13" s="6">
         <f>C12+B6</f>
-        <v>6639.7333333333327</v>
+        <v>6621.3090909090888</v>
       </c>
       <c r="D13" s="6">
         <v>4314</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" si="24"/>
-        <v>6639.7333333333327</v>
+        <v>6621.3090909090888</v>
       </c>
       <c r="F13" s="6">
         <f t="shared" si="25"/>
@@ -7013,7 +6996,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="26"/>
-        <v>-66.662222222222169</v>
+        <v>-66.355151515151505</v>
       </c>
       <c r="H13" s="6">
         <f t="shared" si="35"/>
@@ -7021,7 +7004,7 @@
       </c>
       <c r="I13" s="6">
         <f t="shared" ref="I13" si="54">G13</f>
-        <v>-66.662222222222169</v>
+        <v>-66.355151515151505</v>
       </c>
       <c r="K13" s="6">
         <f t="shared" si="28"/>
@@ -7032,14 +7015,14 @@
       </c>
       <c r="M13" s="6">
         <f>M12+L5</f>
-        <v>6645.3000000000011</v>
+        <v>6615.0600000000013</v>
       </c>
       <c r="N13" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O13" s="6">
         <f t="shared" si="12"/>
-        <v>6645.3000000000011</v>
+        <v>6615.0600000000013</v>
       </c>
       <c r="P13" s="6">
         <f t="shared" si="13"/>
@@ -7047,7 +7030,7 @@
       </c>
       <c r="Q13" s="6">
         <f t="shared" si="14"/>
-        <v>-66.754999999999995</v>
+        <v>-66.251000000000005</v>
       </c>
       <c r="R13" s="6">
         <f t="shared" si="29"/>
@@ -7055,7 +7038,7 @@
       </c>
       <c r="S13" s="6">
         <f t="shared" ref="S13" si="55">Q13</f>
-        <v>-66.754999999999995</v>
+        <v>-66.251000000000005</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="31"/>
@@ -7063,22 +7046,22 @@
       </c>
       <c r="V13" s="6">
         <f>V12+$V5</f>
-        <v>4517.8179999999984</v>
+        <v>4506.4463636363625</v>
       </c>
       <c r="W13" s="6">
         <v>6514</v>
       </c>
       <c r="X13" s="6">
         <f t="shared" ref="X13:Y13" si="56">X12+X5</f>
-        <v>4524.4269999999979</v>
+        <v>4516.0968181818171</v>
       </c>
       <c r="Y13" s="6">
         <f t="shared" si="56"/>
-        <v>6458.1359999999986</v>
+        <v>6445.5745454545468</v>
       </c>
       <c r="Z13" s="6">
         <f t="shared" si="16"/>
-        <v>45.29696666666667</v>
+        <v>45.10743939393933</v>
       </c>
       <c r="AA13" s="6">
         <f t="shared" si="17"/>
@@ -7086,11 +7069,11 @@
       </c>
       <c r="AB13" s="6">
         <f t="shared" si="18"/>
-        <v>45.407116666666667</v>
+        <v>45.26828030303033</v>
       </c>
       <c r="AC13" s="6">
         <f t="shared" si="19"/>
-        <v>-64.968933333333339</v>
+        <v>-64.759575757575831</v>
       </c>
       <c r="AE13" s="8" t="s">
         <v>29</v>
@@ -7106,14 +7089,14 @@
       </c>
       <c r="C14" s="6">
         <f>C13+B6</f>
-        <v>6644.7999999999993</v>
+        <v>6622.6909090909066</v>
       </c>
       <c r="D14" s="6">
         <v>4314</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" si="24"/>
-        <v>6644.7999999999993</v>
+        <v>6622.6909090909066</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="25"/>
@@ -7121,7 +7104,7 @@
       </c>
       <c r="G14" s="6">
         <f t="shared" si="26"/>
-        <v>-66.74666666666667</v>
+        <v>-66.378181818181829</v>
       </c>
       <c r="H14" s="6">
         <f t="shared" si="35"/>
@@ -7129,7 +7112,7 @@
       </c>
       <c r="I14" s="6">
         <f t="shared" ref="I14" si="57">G14</f>
-        <v>-66.74666666666667</v>
+        <v>-66.378181818181829</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="28"/>
@@ -7140,14 +7123,14 @@
       </c>
       <c r="M14" s="6">
         <f>M13+L5</f>
-        <v>6651.6000000000013</v>
+        <v>6616.3200000000015</v>
       </c>
       <c r="N14" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O14" s="6">
         <f t="shared" si="12"/>
-        <v>6651.6000000000013</v>
+        <v>6616.3200000000015</v>
       </c>
       <c r="P14" s="6">
         <f t="shared" si="13"/>
@@ -7155,7 +7138,7 @@
       </c>
       <c r="Q14" s="6">
         <f t="shared" si="14"/>
-        <v>-66.86</v>
+        <v>-66.272000000000006</v>
       </c>
       <c r="R14" s="6">
         <f t="shared" si="29"/>
@@ -7163,7 +7146,7 @@
       </c>
       <c r="S14" s="6">
         <f t="shared" ref="S14" si="58">Q14</f>
-        <v>-66.86</v>
+        <v>-66.272000000000006</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="31"/>
@@ -7171,22 +7154,22 @@
       </c>
       <c r="V14" s="6">
         <f>V13+$V5</f>
-        <v>4520.4239999999982</v>
+        <v>4507.1570909090897</v>
       </c>
       <c r="W14" s="6">
         <v>6514</v>
       </c>
       <c r="X14" s="6">
         <f t="shared" ref="X14:Y14" si="59">X13+X5</f>
-        <v>4526.3359999999975</v>
+        <v>4516.6174545454533</v>
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="59"/>
-        <v>6461.0146666666651</v>
+        <v>6446.3596363636379</v>
       </c>
       <c r="Z14" s="6">
         <f t="shared" si="16"/>
-        <v>45.340400000000002</v>
+        <v>45.119284848484831</v>
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="17"/>
@@ -7194,11 +7177,11 @@
       </c>
       <c r="AB14" s="6">
         <f t="shared" si="18"/>
-        <v>45.438933333333331</v>
+        <v>45.2769575757575</v>
       </c>
       <c r="AC14" s="6">
         <f t="shared" si="19"/>
-        <v>-65.01691111111117</v>
+        <v>-64.772660606060668</v>
       </c>
       <c r="AE14" s="6" t="s">
         <v>21</v>
@@ -7238,14 +7221,14 @@
       </c>
       <c r="C15" s="6">
         <f>C14+B6</f>
-        <v>6649.8666666666659</v>
+        <v>6624.0727272727245</v>
       </c>
       <c r="D15" s="6">
         <v>4314</v>
       </c>
       <c r="E15" s="6">
         <f t="shared" si="24"/>
-        <v>6649.8666666666659</v>
+        <v>6624.0727272727245</v>
       </c>
       <c r="F15" s="6">
         <f t="shared" si="25"/>
@@ -7253,7 +7236,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="26"/>
-        <v>-66.83111111111117</v>
+        <v>-66.401212121211998</v>
       </c>
       <c r="H15" s="6">
         <f t="shared" si="35"/>
@@ -7261,7 +7244,7 @@
       </c>
       <c r="I15" s="6">
         <f t="shared" ref="I15" si="60">G15</f>
-        <v>-66.83111111111117</v>
+        <v>-66.401212121211998</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="28"/>
@@ -7272,14 +7255,14 @@
       </c>
       <c r="M15" s="6">
         <f>M14+L5</f>
-        <v>6657.9000000000015</v>
+        <v>6617.5800000000017</v>
       </c>
       <c r="N15" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O15" s="6">
         <f t="shared" si="12"/>
-        <v>6657.9000000000015</v>
+        <v>6617.5800000000017</v>
       </c>
       <c r="P15" s="6">
         <f t="shared" si="13"/>
@@ -7287,7 +7270,7 @@
       </c>
       <c r="Q15" s="6">
         <f t="shared" si="14"/>
-        <v>-66.965000000000003</v>
+        <v>-66.293000000000006</v>
       </c>
       <c r="R15" s="6">
         <f t="shared" si="29"/>
@@ -7295,7 +7278,7 @@
       </c>
       <c r="S15" s="6">
         <f t="shared" ref="S15" si="61">Q15</f>
-        <v>-66.965000000000003</v>
+        <v>-66.293000000000006</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="31"/>
@@ -7303,22 +7286,22 @@
       </c>
       <c r="V15" s="6">
         <f>V14+$V5</f>
-        <v>4523.0299999999979</v>
+        <v>4507.8678181818168</v>
       </c>
       <c r="W15" s="6">
         <v>6514</v>
       </c>
       <c r="X15" s="6">
         <f t="shared" ref="X15:Y15" si="62">X14+X5</f>
-        <v>4528.2449999999972</v>
+        <v>4517.1380909090894</v>
       </c>
       <c r="Y15" s="6">
         <f t="shared" si="62"/>
-        <v>6463.8933333333316</v>
+        <v>6447.1447272727291</v>
       </c>
       <c r="Z15" s="6">
         <f t="shared" si="16"/>
-        <v>45.383833333333335</v>
+        <v>45.131130303030332</v>
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="17"/>
@@ -7326,11 +7309,11 @@
       </c>
       <c r="AB15" s="6">
         <f t="shared" si="18"/>
-        <v>45.470750000000002</v>
+        <v>45.285634848484833</v>
       </c>
       <c r="AC15" s="6">
         <f t="shared" si="19"/>
-        <v>-65.064888888888831</v>
+        <v>-64.785745454545506</v>
       </c>
       <c r="AE15" s="6" t="s">
         <v>23</v>
@@ -7360,14 +7343,14 @@
       </c>
       <c r="C16" s="6">
         <f>C15+B6</f>
-        <v>6654.9333333333325</v>
+        <v>6625.4545454545423</v>
       </c>
       <c r="D16" s="6">
         <v>4314</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" si="24"/>
-        <v>6654.9333333333325</v>
+        <v>6625.4545454545423</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="25"/>
@@ -7375,7 +7358,7 @@
       </c>
       <c r="G16" s="6">
         <f t="shared" si="26"/>
-        <v>-66.9155555555555</v>
+        <v>-66.424242424242337</v>
       </c>
       <c r="H16" s="6">
         <f t="shared" si="35"/>
@@ -7383,7 +7366,7 @@
       </c>
       <c r="I16" s="6">
         <f t="shared" ref="I16" si="63">G16</f>
-        <v>-66.9155555555555</v>
+        <v>-66.424242424242337</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="28"/>
@@ -7394,14 +7377,14 @@
       </c>
       <c r="M16" s="6">
         <f>M15+L5</f>
-        <v>6664.2000000000016</v>
+        <v>6618.840000000002</v>
       </c>
       <c r="N16" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O16" s="6">
         <f t="shared" si="12"/>
-        <v>6664.2000000000016</v>
+        <v>6618.840000000002</v>
       </c>
       <c r="P16" s="6">
         <f t="shared" si="13"/>
@@ -7409,7 +7392,7 @@
       </c>
       <c r="Q16" s="6">
         <f t="shared" si="14"/>
-        <v>-67.069999999999993</v>
+        <v>-66.313999999999993</v>
       </c>
       <c r="R16" s="6">
         <f t="shared" si="29"/>
@@ -7417,7 +7400,7 @@
       </c>
       <c r="S16" s="6">
         <f t="shared" ref="S16" si="64">Q16</f>
-        <v>-67.069999999999993</v>
+        <v>-66.313999999999993</v>
       </c>
       <c r="U16" s="6">
         <f t="shared" si="31"/>
@@ -7425,22 +7408,22 @@
       </c>
       <c r="V16" s="6">
         <f>V15+$V5</f>
-        <v>4525.6359999999977</v>
+        <v>4508.5785454545439</v>
       </c>
       <c r="W16" s="6">
         <v>6514</v>
       </c>
       <c r="X16" s="6">
         <f t="shared" ref="X16:Y16" si="65">X15+X5</f>
-        <v>4530.1539999999968</v>
+        <v>4517.6587272727256</v>
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="65"/>
-        <v>6466.7719999999981</v>
+        <v>6447.9298181818203</v>
       </c>
       <c r="Z16" s="6">
         <f t="shared" si="16"/>
-        <v>45.427266666666668</v>
+        <v>45.14297575757567</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="17"/>
@@ -7448,11 +7431,11 @@
       </c>
       <c r="AB16" s="6">
         <f t="shared" si="18"/>
-        <v>45.502566666666667</v>
+        <v>45.294312121212165</v>
       </c>
       <c r="AC16" s="6">
         <f t="shared" si="19"/>
-        <v>-65.112866666666662</v>
+        <v>-64.798830303030329</v>
       </c>
       <c r="AE16" s="6" t="s">
         <v>24</v>
@@ -7489,14 +7472,14 @@
       </c>
       <c r="C17" s="6">
         <f>C16+B6</f>
-        <v>6659.9999999999991</v>
+        <v>6626.8363636363601</v>
       </c>
       <c r="D17" s="6">
         <v>4314</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" si="24"/>
-        <v>6659.9999999999991</v>
+        <v>6626.8363636363601</v>
       </c>
       <c r="F17" s="6">
         <f t="shared" si="25"/>
@@ -7504,7 +7487,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="26"/>
-        <v>-67</v>
+        <v>-66.447272727272662</v>
       </c>
       <c r="H17" s="6">
         <f t="shared" si="35"/>
@@ -7512,7 +7495,7 @@
       </c>
       <c r="I17" s="6">
         <f t="shared" ref="I17" si="67">G17</f>
-        <v>-67</v>
+        <v>-66.447272727272662</v>
       </c>
       <c r="K17" s="6">
         <f t="shared" si="28"/>
@@ -7523,14 +7506,14 @@
       </c>
       <c r="M17" s="6">
         <f>M16+L5</f>
-        <v>6670.5000000000018</v>
+        <v>6620.1000000000022</v>
       </c>
       <c r="N17" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O17" s="6">
         <f t="shared" si="12"/>
-        <v>6670.5000000000018</v>
+        <v>6620.1000000000022</v>
       </c>
       <c r="P17" s="6">
         <f t="shared" si="13"/>
@@ -7538,7 +7521,7 @@
       </c>
       <c r="Q17" s="6">
         <f t="shared" si="14"/>
-        <v>-67.174999999999997</v>
+        <v>-66.334999999999994</v>
       </c>
       <c r="R17" s="6">
         <f t="shared" si="29"/>
@@ -7546,7 +7529,7 @@
       </c>
       <c r="S17" s="6">
         <f t="shared" ref="S17" si="68">Q17</f>
-        <v>-67.174999999999997</v>
+        <v>-66.334999999999994</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="31"/>
@@ -7554,22 +7537,22 @@
       </c>
       <c r="V17" s="6">
         <f>V16+$V5</f>
-        <v>4528.2419999999975</v>
+        <v>4509.2892727272711</v>
       </c>
       <c r="W17" s="6">
         <v>6514</v>
       </c>
       <c r="X17" s="6">
         <f t="shared" ref="X17:Y17" si="69">X16+X5</f>
-        <v>4532.0629999999965</v>
+        <v>4518.1793636363618</v>
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="69"/>
-        <v>6469.6506666666646</v>
+        <v>6448.7149090909115</v>
       </c>
       <c r="Z17" s="6">
         <f t="shared" si="16"/>
-        <v>45.470700000000001</v>
+        <v>45.154821212121163</v>
       </c>
       <c r="AA17" s="6">
         <f t="shared" si="17"/>
@@ -7577,11 +7560,11 @@
       </c>
       <c r="AB17" s="6">
         <f t="shared" si="18"/>
-        <v>45.534383333333331</v>
+        <v>45.302989393939335</v>
       </c>
       <c r="AC17" s="6">
         <f t="shared" si="19"/>
-        <v>-65.160844444444336</v>
+        <v>-64.811915151515166</v>
       </c>
       <c r="AE17" s="6" t="s">
         <v>25</v>
@@ -7621,14 +7604,14 @@
       </c>
       <c r="C18" s="6">
         <f>C17+B6</f>
-        <v>6665.0666666666657</v>
+        <v>6628.218181818178</v>
       </c>
       <c r="D18" s="6">
         <v>4314</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="24"/>
-        <v>6665.0666666666657</v>
+        <v>6628.218181818178</v>
       </c>
       <c r="F18" s="6">
         <f t="shared" si="25"/>
@@ -7636,7 +7619,7 @@
       </c>
       <c r="G18" s="6">
         <f t="shared" si="26"/>
-        <v>-67.0844444444445</v>
+        <v>-66.470303030303</v>
       </c>
       <c r="H18" s="6">
         <f t="shared" si="35"/>
@@ -7644,7 +7627,7 @@
       </c>
       <c r="I18" s="6">
         <f t="shared" ref="I18" si="70">G18</f>
-        <v>-67.0844444444445</v>
+        <v>-66.470303030303</v>
       </c>
       <c r="K18" s="6">
         <f t="shared" si="28"/>
@@ -7655,14 +7638,14 @@
       </c>
       <c r="M18" s="6">
         <f>M17+L5</f>
-        <v>6676.800000000002</v>
+        <v>6621.3600000000024</v>
       </c>
       <c r="N18" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O18" s="6">
         <f t="shared" si="12"/>
-        <v>6676.800000000002</v>
+        <v>6621.3600000000024</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="13"/>
@@ -7670,7 +7653,7 @@
       </c>
       <c r="Q18" s="6">
         <f t="shared" si="14"/>
-        <v>-67.28</v>
+        <v>-66.355999999999995</v>
       </c>
       <c r="R18" s="6">
         <f t="shared" si="29"/>
@@ -7678,7 +7661,7 @@
       </c>
       <c r="S18" s="6">
         <f t="shared" ref="S18" si="71">Q18</f>
-        <v>-67.28</v>
+        <v>-66.355999999999995</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="31"/>
@@ -7686,22 +7669,22 @@
       </c>
       <c r="V18" s="6">
         <f>V17+$V5</f>
-        <v>4530.8479999999972</v>
+        <v>4509.9999999999982</v>
       </c>
       <c r="W18" s="6">
         <v>6514</v>
       </c>
       <c r="X18" s="9">
         <f t="shared" ref="X18:Y18" si="72">X17+X5</f>
-        <v>4533.9719999999961</v>
+        <v>4518.699999999998</v>
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="72"/>
-        <v>6472.5293333333311</v>
+        <v>6449.5000000000027</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="16"/>
-        <v>45.514133333333334</v>
+        <v>45.166666666666664</v>
       </c>
       <c r="AA18" s="6">
         <f t="shared" si="17"/>
@@ -7709,11 +7692,11 @@
       </c>
       <c r="AB18" s="6">
         <f t="shared" si="18"/>
-        <v>45.566200000000002</v>
+        <v>45.311666666666667</v>
       </c>
       <c r="AC18" s="6">
         <f t="shared" si="19"/>
-        <v>-65.208822222222167</v>
+        <v>-64.825000000000003</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>27</v>
@@ -7741,14 +7724,14 @@
       </c>
       <c r="C19" s="6">
         <f>C18+B6</f>
-        <v>6670.1333333333323</v>
+        <v>6629.5999999999958</v>
       </c>
       <c r="D19" s="6">
         <v>4314</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="24"/>
-        <v>6670.1333333333323</v>
+        <v>6629.5999999999958</v>
       </c>
       <c r="F19" s="6">
         <f t="shared" si="25"/>
@@ -7756,7 +7739,7 @@
       </c>
       <c r="G19" s="6">
         <f t="shared" si="26"/>
-        <v>-67.16888888888883</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="H19" s="6">
         <f t="shared" si="35"/>
@@ -7764,7 +7747,7 @@
       </c>
       <c r="I19" s="6">
         <f t="shared" ref="I19" si="73">G19</f>
-        <v>-67.16888888888883</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="K19" s="6">
         <f t="shared" si="28"/>
@@ -7775,14 +7758,14 @@
       </c>
       <c r="M19" s="6">
         <f>M18+L5</f>
-        <v>6683.1000000000022</v>
+        <v>6622.6200000000026</v>
       </c>
       <c r="N19" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O19" s="6">
         <f t="shared" si="12"/>
-        <v>6683.1000000000022</v>
+        <v>6622.6200000000026</v>
       </c>
       <c r="P19" s="6">
         <f t="shared" si="13"/>
@@ -7790,7 +7773,7 @@
       </c>
       <c r="Q19" s="6">
         <f t="shared" si="14"/>
-        <v>-67.385000000000005</v>
+        <v>-66.376999999999995</v>
       </c>
       <c r="R19" s="6">
         <f t="shared" si="29"/>
@@ -7798,7 +7781,7 @@
       </c>
       <c r="S19" s="6">
         <f t="shared" ref="S19" si="74">Q19</f>
-        <v>-67.385000000000005</v>
+        <v>-66.376999999999995</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="31"/>
@@ -7806,22 +7789,22 @@
       </c>
       <c r="V19" s="6">
         <f>V18+$V5</f>
-        <v>4533.453999999997</v>
+        <v>4510.7107272727253</v>
       </c>
       <c r="W19" s="6">
         <v>6514</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" ref="X19:Y19" si="75">X18+X5</f>
-        <v>4535.8809999999958</v>
+        <v>4519.2206363636342</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="75"/>
-        <v>6475.4079999999976</v>
+        <v>6450.2850909090939</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="16"/>
-        <v>45.557566666666666</v>
+        <v>45.178512121212165</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="17"/>
@@ -7829,11 +7812,11 @@
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="18"/>
-        <v>45.598016666666666</v>
+        <v>45.320343939393837</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="19"/>
-        <v>-65.256799999999998</v>
+        <v>-64.83808484848484</v>
       </c>
       <c r="AE19" s="6">
         <v>1</v>
@@ -7877,14 +7860,14 @@
       </c>
       <c r="C20" s="6">
         <f>C19+B6</f>
-        <v>6675.1999999999989</v>
+        <v>6630.9818181818137</v>
       </c>
       <c r="D20" s="6">
         <v>4314</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="24"/>
-        <v>6675.1999999999989</v>
+        <v>6630.9818181818137</v>
       </c>
       <c r="F20" s="6">
         <f t="shared" si="25"/>
@@ -7892,7 +7875,7 @@
       </c>
       <c r="G20" s="6">
         <f t="shared" si="26"/>
-        <v>-67.25333333333333</v>
+        <v>-66.516363636363494</v>
       </c>
       <c r="H20" s="6">
         <f t="shared" si="35"/>
@@ -7900,7 +7883,7 @@
       </c>
       <c r="I20" s="6">
         <f t="shared" ref="I20" si="77">G20</f>
-        <v>-67.25333333333333</v>
+        <v>-66.516363636363494</v>
       </c>
       <c r="K20" s="6">
         <f t="shared" si="28"/>
@@ -7911,14 +7894,14 @@
       </c>
       <c r="M20" s="6">
         <f>M19+L5</f>
-        <v>6689.4000000000024</v>
+        <v>6623.8800000000028</v>
       </c>
       <c r="N20" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O20" s="6">
         <f t="shared" si="12"/>
-        <v>6689.4000000000024</v>
+        <v>6623.8800000000028</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="13"/>
@@ -7926,7 +7909,7 @@
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="14"/>
-        <v>-67.489999999999995</v>
+        <v>-66.397999999999996</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="29"/>
@@ -7934,7 +7917,7 @@
       </c>
       <c r="S20" s="6">
         <f t="shared" ref="S20" si="78">Q20</f>
-        <v>-67.489999999999995</v>
+        <v>-66.397999999999996</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="31"/>
@@ -7942,22 +7925,22 @@
       </c>
       <c r="V20" s="6">
         <f>V19+$V5</f>
-        <v>4536.0599999999968</v>
+        <v>4511.4214545454524</v>
       </c>
       <c r="W20" s="6">
         <v>6514</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" ref="X20:Y20" si="79">X19+X5</f>
-        <v>4537.7899999999954</v>
+        <v>4519.7412727272704</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="79"/>
-        <v>6478.2866666666641</v>
+        <v>6451.0701818181851</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="16"/>
-        <v>45.600999999999999</v>
+        <v>45.190357575757503</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="17"/>
@@ -7965,11 +7948,11 @@
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="18"/>
-        <v>45.62983333333333</v>
+        <v>45.32902121212117</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="19"/>
-        <v>-65.304777777777673</v>
+        <v>-64.851169696969833</v>
       </c>
       <c r="AE20" s="6">
         <v>2</v>
@@ -8013,14 +7996,14 @@
       </c>
       <c r="C21" s="6">
         <f>C20+B6</f>
-        <v>6680.2666666666655</v>
+        <v>6632.3636363636315</v>
       </c>
       <c r="D21" s="6">
         <v>4314</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" si="24"/>
-        <v>6680.2666666666655</v>
+        <v>6632.3636363636315</v>
       </c>
       <c r="F21" s="6">
         <f t="shared" si="25"/>
@@ -8028,7 +8011,7 @@
       </c>
       <c r="G21" s="6">
         <f t="shared" si="26"/>
-        <v>-67.337777777777831</v>
+        <v>-66.539393939393833</v>
       </c>
       <c r="H21" s="6">
         <f t="shared" si="35"/>
@@ -8036,7 +8019,7 @@
       </c>
       <c r="I21" s="6">
         <f t="shared" ref="I21" si="83">G21</f>
-        <v>-67.337777777777831</v>
+        <v>-66.539393939393833</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="28"/>
@@ -8047,14 +8030,14 @@
       </c>
       <c r="M21" s="6">
         <f>M20+L5</f>
-        <v>6695.7000000000025</v>
+        <v>6625.1400000000031</v>
       </c>
       <c r="N21" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O21" s="6">
         <f t="shared" si="12"/>
-        <v>6695.7000000000025</v>
+        <v>6625.1400000000031</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="13"/>
@@ -8062,7 +8045,7 @@
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="14"/>
-        <v>-67.594999999999999</v>
+        <v>-66.418999999999997</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="29"/>
@@ -8070,7 +8053,7 @@
       </c>
       <c r="S21" s="6">
         <f t="shared" ref="S21" si="84">Q21</f>
-        <v>-67.594999999999999</v>
+        <v>-66.418999999999997</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="31"/>
@@ -8078,22 +8061,22 @@
       </c>
       <c r="V21" s="6">
         <f>V20+$V5</f>
-        <v>4538.6659999999965</v>
+        <v>4512.1321818181796</v>
       </c>
       <c r="W21" s="6">
         <v>6514</v>
       </c>
       <c r="X21" s="6">
         <f t="shared" ref="X21:Y21" si="85">X20+X5</f>
-        <v>4539.6989999999951</v>
+        <v>4520.2619090909066</v>
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="85"/>
-        <v>6481.1653333333306</v>
+        <v>6451.8552727272763</v>
       </c>
       <c r="Z21" s="6">
         <f t="shared" si="16"/>
-        <v>45.644433333333332</v>
+        <v>45.202203030302996</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="17"/>
@@ -8101,11 +8084,11 @@
       </c>
       <c r="AB21" s="6">
         <f t="shared" si="18"/>
-        <v>45.661650000000002</v>
+        <v>45.337698484848502</v>
       </c>
       <c r="AC21" s="6">
         <f t="shared" si="19"/>
-        <v>-65.352755555555504</v>
+        <v>-64.864254545454671</v>
       </c>
       <c r="AE21" s="6">
         <v>3</v>
@@ -8149,14 +8132,14 @@
       </c>
       <c r="C22" s="6">
         <f>C21+B6</f>
-        <v>6685.3333333333321</v>
+        <v>6633.7454545454493</v>
       </c>
       <c r="D22" s="6">
         <v>4314</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="24"/>
-        <v>6685.3333333333321</v>
+        <v>6633.7454545454493</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="25"/>
@@ -8164,7 +8147,7 @@
       </c>
       <c r="G22" s="6">
         <f t="shared" si="26"/>
-        <v>-67.42222222222216</v>
+        <v>-66.562424242424171</v>
       </c>
       <c r="H22" s="6">
         <f t="shared" si="35"/>
@@ -8172,7 +8155,7 @@
       </c>
       <c r="I22" s="6">
         <f t="shared" ref="I22" si="86">G22</f>
-        <v>-67.42222222222216</v>
+        <v>-66.562424242424171</v>
       </c>
       <c r="K22" s="6">
         <f t="shared" si="28"/>
@@ -8183,14 +8166,14 @@
       </c>
       <c r="M22" s="6">
         <f>M21+L5</f>
-        <v>6702.0000000000027</v>
+        <v>6626.4000000000033</v>
       </c>
       <c r="N22" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O22" s="6">
         <f t="shared" si="12"/>
-        <v>6702.0000000000027</v>
+        <v>6626.4000000000033</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" si="13"/>
@@ -8198,7 +8181,7 @@
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="14"/>
-        <v>-67.033333333333331</v>
+        <v>-66.44</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="29"/>
@@ -8206,7 +8189,7 @@
       </c>
       <c r="S22" s="6">
         <f t="shared" ref="S22" si="87">Q22</f>
-        <v>-67.033333333333331</v>
+        <v>-66.44</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="31"/>
@@ -8214,22 +8197,22 @@
       </c>
       <c r="V22" s="6">
         <f>V21+$V5</f>
-        <v>4541.2719999999963</v>
+        <v>4512.8429090909067</v>
       </c>
       <c r="W22" s="6">
         <v>6514</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" ref="X22:Y22" si="88">X21+X5</f>
-        <v>4541.6079999999947</v>
+        <v>4520.7825454545427</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="88"/>
-        <v>6484.0439999999971</v>
+        <v>6452.6403636363675</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="16"/>
-        <v>45.687866666666665</v>
+        <v>45.214048484848497</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="17"/>
@@ -8237,11 +8220,11 @@
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="18"/>
-        <v>45.693466666666502</v>
+        <v>45.346375757575665</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="19"/>
-        <v>-65.400733333333335</v>
+        <v>-64.877339393939494</v>
       </c>
       <c r="AE22" s="6">
         <v>4</v>
@@ -8285,14 +8268,14 @@
       </c>
       <c r="C23" s="6">
         <f>C22+B6</f>
-        <v>6690.3999999999987</v>
+        <v>6635.1272727272672</v>
       </c>
       <c r="D23" s="6">
         <v>4314</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="24"/>
-        <v>6690.3999999999987</v>
+        <v>6635.1272727272672</v>
       </c>
       <c r="F23" s="6">
         <f t="shared" si="25"/>
@@ -8300,7 +8283,7 @@
       </c>
       <c r="G23" s="6">
         <f t="shared" si="26"/>
-        <v>-67.506666666666661</v>
+        <v>-66.585454545454496</v>
       </c>
       <c r="H23" s="6">
         <f t="shared" si="35"/>
@@ -8308,7 +8291,7 @@
       </c>
       <c r="I23" s="6">
         <f t="shared" ref="I23" si="89">G23</f>
-        <v>-67.506666666666661</v>
+        <v>-66.585454545454496</v>
       </c>
       <c r="K23" s="6">
         <f t="shared" si="28"/>
@@ -8319,14 +8302,14 @@
       </c>
       <c r="M23" s="6">
         <f>M22+L5</f>
-        <v>6708.3000000000029</v>
+        <v>6627.6600000000035</v>
       </c>
       <c r="N23" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O23" s="6">
         <f t="shared" si="12"/>
-        <v>6708.3000000000029</v>
+        <v>6627.6600000000035</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="13"/>
@@ -8334,7 +8317,7 @@
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="14"/>
-        <v>-67.138333333333335</v>
+        <v>-66.460999999999999</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="29"/>
@@ -8342,7 +8325,7 @@
       </c>
       <c r="S23" s="6">
         <f t="shared" ref="S23" si="90">Q23</f>
-        <v>-67.138333333333335</v>
+        <v>-66.460999999999999</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="31"/>
@@ -8350,22 +8333,22 @@
       </c>
       <c r="V23" s="6">
         <f>V22+$V5</f>
-        <v>4543.8779999999961</v>
+        <v>4513.5536363636338</v>
       </c>
       <c r="W23" s="6">
         <v>6514</v>
       </c>
       <c r="X23" s="6">
         <f t="shared" ref="X23:Y23" si="91">X22+X5</f>
-        <v>4543.5169999999944</v>
+        <v>4521.3031818181789</v>
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="91"/>
-        <v>6486.9226666666636</v>
+        <v>6453.4254545454587</v>
       </c>
       <c r="Z23" s="6">
         <f t="shared" si="16"/>
-        <v>45.731299999999997</v>
+        <v>45.225893939393835</v>
       </c>
       <c r="AA23" s="6">
         <f t="shared" si="17"/>
@@ -8373,11 +8356,11 @@
       </c>
       <c r="AB23" s="6">
         <f t="shared" si="18"/>
-        <v>45.725283333333167</v>
+        <v>45.355053030302997</v>
       </c>
       <c r="AC23" s="6">
         <f t="shared" si="19"/>
-        <v>-65.448711111110995</v>
+        <v>-64.890424242424331</v>
       </c>
       <c r="AE23" s="6" t="s">
         <v>28</v>
@@ -8417,14 +8400,14 @@
       </c>
       <c r="C24" s="6">
         <f>C23+B6</f>
-        <v>6695.4666666666653</v>
+        <v>6636.509090909085</v>
       </c>
       <c r="D24" s="6">
         <v>4314</v>
       </c>
       <c r="E24" s="6">
         <f t="shared" si="24"/>
-        <v>6695.4666666666653</v>
+        <v>6636.509090909085</v>
       </c>
       <c r="F24" s="6">
         <f t="shared" si="25"/>
@@ -8432,7 +8415,7 @@
       </c>
       <c r="G24" s="6">
         <f t="shared" si="26"/>
-        <v>-67.591111111111161</v>
+        <v>-66.608484848484665</v>
       </c>
       <c r="H24" s="6">
         <f t="shared" si="35"/>
@@ -8440,7 +8423,7 @@
       </c>
       <c r="I24" s="6">
         <f t="shared" ref="I24" si="92">G24</f>
-        <v>-67.591111111111161</v>
+        <v>-66.608484848484665</v>
       </c>
       <c r="K24" s="6">
         <f t="shared" si="28"/>
@@ -8451,14 +8434,14 @@
       </c>
       <c r="M24" s="6">
         <f>M23+L5</f>
-        <v>6714.6000000000031</v>
+        <v>6628.9200000000037</v>
       </c>
       <c r="N24" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O24" s="6">
         <f t="shared" si="12"/>
-        <v>6714.6000000000031</v>
+        <v>6628.9200000000037</v>
       </c>
       <c r="P24" s="6">
         <f t="shared" si="13"/>
@@ -8466,7 +8449,7 @@
       </c>
       <c r="Q24" s="6">
         <f t="shared" si="14"/>
-        <v>-67.243333333333339</v>
+        <v>-66.481999999999999</v>
       </c>
       <c r="R24" s="6">
         <f t="shared" si="29"/>
@@ -8474,7 +8457,7 @@
       </c>
       <c r="S24" s="6">
         <f t="shared" ref="S24" si="93">Q24</f>
-        <v>-67.243333333333339</v>
+        <v>-66.481999999999999</v>
       </c>
       <c r="U24" s="6">
         <f t="shared" si="31"/>
@@ -8482,22 +8465,22 @@
       </c>
       <c r="V24" s="6">
         <f>V23+$V5</f>
-        <v>4546.4839999999958</v>
+        <v>4514.2643636363609</v>
       </c>
       <c r="W24" s="6">
         <v>6514</v>
       </c>
       <c r="X24" s="6">
         <f t="shared" ref="X24:Y24" si="94">X23+X5</f>
-        <v>4545.425999999994</v>
+        <v>4521.8238181818151</v>
       </c>
       <c r="Y24" s="6">
         <f t="shared" si="94"/>
-        <v>6489.8013333333301</v>
+        <v>6454.2105454545499</v>
       </c>
       <c r="Z24" s="6">
         <f t="shared" si="16"/>
-        <v>45.77473333333333</v>
+        <v>45.237739393939336</v>
       </c>
       <c r="AA24" s="6">
         <f t="shared" si="17"/>
@@ -8505,11 +8488,11 @@
       </c>
       <c r="AB24" s="6">
         <f t="shared" si="18"/>
-        <v>45.757099999999831</v>
+        <v>45.36373030303033</v>
       </c>
       <c r="AC24" s="6">
         <f t="shared" si="19"/>
-        <v>-65.496688888888826</v>
+        <v>-64.903509090909168</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8522,14 +8505,14 @@
       </c>
       <c r="C25" s="6">
         <f>C24+B6</f>
-        <v>6700.5333333333319</v>
+        <v>6637.8909090909028</v>
       </c>
       <c r="D25" s="6">
         <v>4314</v>
       </c>
       <c r="E25" s="6">
         <f t="shared" si="24"/>
-        <v>6700.5333333333319</v>
+        <v>6637.8909090909028</v>
       </c>
       <c r="F25" s="6">
         <f t="shared" si="25"/>
@@ -8537,7 +8520,7 @@
       </c>
       <c r="G25" s="6">
         <f t="shared" si="26"/>
-        <v>-67.008888888888833</v>
+        <v>-66.631515151515003</v>
       </c>
       <c r="H25" s="6">
         <f t="shared" si="35"/>
@@ -8545,7 +8528,7 @@
       </c>
       <c r="I25" s="6">
         <f t="shared" ref="I25" si="95">G25</f>
-        <v>-67.008888888888833</v>
+        <v>-66.631515151515003</v>
       </c>
       <c r="K25" s="6">
         <f t="shared" si="28"/>
@@ -8556,14 +8539,14 @@
       </c>
       <c r="M25" s="6">
         <f>M24+L5</f>
-        <v>6720.9000000000033</v>
+        <v>6630.1800000000039</v>
       </c>
       <c r="N25" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O25" s="6">
         <f t="shared" si="12"/>
-        <v>6720.9000000000033</v>
+        <v>6630.1800000000039</v>
       </c>
       <c r="P25" s="6">
         <f t="shared" si="13"/>
@@ -8571,7 +8554,7 @@
       </c>
       <c r="Q25" s="6">
         <f t="shared" si="14"/>
-        <v>-67.348333333333329</v>
+        <v>-66.503</v>
       </c>
       <c r="R25" s="6">
         <f t="shared" si="29"/>
@@ -8579,7 +8562,7 @@
       </c>
       <c r="S25" s="6">
         <f t="shared" ref="S25" si="96">Q25</f>
-        <v>-67.348333333333329</v>
+        <v>-66.503</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>28</v>
@@ -8623,14 +8606,14 @@
       </c>
       <c r="C26" s="6">
         <f>C25+B6</f>
-        <v>6705.5999999999985</v>
+        <v>6639.2727272727207</v>
       </c>
       <c r="D26" s="6">
         <v>4314</v>
       </c>
       <c r="E26" s="6">
         <f t="shared" si="24"/>
-        <v>6705.5999999999985</v>
+        <v>6639.2727272727207</v>
       </c>
       <c r="F26" s="6">
         <f t="shared" si="25"/>
@@ -8638,7 +8621,7 @@
       </c>
       <c r="G26" s="6">
         <f t="shared" si="26"/>
-        <v>-67.093333333333334</v>
+        <v>-66.654545454545328</v>
       </c>
       <c r="H26" s="6">
         <f t="shared" si="35"/>
@@ -8646,7 +8629,7 @@
       </c>
       <c r="I26" s="6">
         <f t="shared" ref="I26" si="97">G26</f>
-        <v>-67.093333333333334</v>
+        <v>-66.654545454545328</v>
       </c>
       <c r="K26" s="6">
         <f t="shared" si="28"/>
@@ -8657,14 +8640,14 @@
       </c>
       <c r="M26" s="6">
         <f>M25+L5</f>
-        <v>6727.2000000000035</v>
+        <v>6631.4400000000041</v>
       </c>
       <c r="N26" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O26" s="6">
         <f t="shared" si="12"/>
-        <v>6727.2000000000035</v>
+        <v>6631.4400000000041</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="13"/>
@@ -8672,7 +8655,7 @@
       </c>
       <c r="Q26" s="6">
         <f t="shared" si="14"/>
-        <v>-67.453333333333333</v>
+        <v>-66.524000000000001</v>
       </c>
       <c r="R26" s="6">
         <f t="shared" si="29"/>
@@ -8680,7 +8663,7 @@
       </c>
       <c r="S26" s="6">
         <f t="shared" ref="S26" si="98">Q26</f>
-        <v>-67.453333333333333</v>
+        <v>-66.524000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8693,14 +8676,14 @@
       </c>
       <c r="C27" s="6">
         <f>C26+B6</f>
-        <v>6710.6666666666652</v>
+        <v>6640.6545454545385</v>
       </c>
       <c r="D27" s="6">
         <v>4314</v>
       </c>
       <c r="E27" s="6">
         <f t="shared" si="24"/>
-        <v>6710.6666666666652</v>
+        <v>6640.6545454545385</v>
       </c>
       <c r="F27" s="6">
         <f t="shared" si="25"/>
@@ -8708,7 +8691,7 @@
       </c>
       <c r="G27" s="6">
         <f t="shared" si="26"/>
-        <v>-67.177777777777834</v>
+        <v>-66.677575757575667</v>
       </c>
       <c r="H27" s="6">
         <f t="shared" si="35"/>
@@ -8716,7 +8699,7 @@
       </c>
       <c r="I27" s="6">
         <f t="shared" ref="I27" si="99">G27</f>
-        <v>-67.177777777777834</v>
+        <v>-66.677575757575667</v>
       </c>
       <c r="K27" s="6">
         <f t="shared" si="28"/>
@@ -8727,14 +8710,14 @@
       </c>
       <c r="M27" s="6">
         <f>M26+L5</f>
-        <v>6733.5000000000036</v>
+        <v>6632.7000000000044</v>
       </c>
       <c r="N27" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O27" s="6">
         <f t="shared" si="12"/>
-        <v>6733.5000000000036</v>
+        <v>6632.7000000000044</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="13"/>
@@ -8742,7 +8725,7 @@
       </c>
       <c r="Q27" s="6">
         <f t="shared" si="14"/>
-        <v>-67.558333333333337</v>
+        <v>-66.545000000000002</v>
       </c>
       <c r="R27" s="6">
         <f t="shared" si="29"/>
@@ -8750,7 +8733,7 @@
       </c>
       <c r="S27" s="6">
         <f t="shared" ref="S27" si="100">Q27</f>
-        <v>-67.558333333333337</v>
+        <v>-66.545000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8763,14 +8746,14 @@
       </c>
       <c r="C28" s="6">
         <f>C27+B6</f>
-        <v>6715.7333333333318</v>
+        <v>6642.0363636363563</v>
       </c>
       <c r="D28" s="6">
         <v>4314</v>
       </c>
       <c r="E28" s="6">
         <f t="shared" si="24"/>
-        <v>6715.7333333333318</v>
+        <v>6642.0363636363563</v>
       </c>
       <c r="F28" s="6">
         <f t="shared" si="25"/>
@@ -8778,7 +8761,7 @@
       </c>
       <c r="G28" s="6">
         <f t="shared" si="26"/>
-        <v>-67.262222222222164</v>
+        <v>-66.700606060606006</v>
       </c>
       <c r="H28" s="6">
         <f t="shared" si="35"/>
@@ -8786,7 +8769,7 @@
       </c>
       <c r="I28" s="6">
         <f t="shared" ref="I28" si="101">G28</f>
-        <v>-67.262222222222164</v>
+        <v>-66.700606060606006</v>
       </c>
       <c r="K28" s="6">
         <f t="shared" si="28"/>
@@ -8797,14 +8780,14 @@
       </c>
       <c r="M28" s="6">
         <f>M27+L5</f>
-        <v>6739.8000000000038</v>
+        <v>6633.9600000000046</v>
       </c>
       <c r="N28" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O28" s="6">
         <f t="shared" si="12"/>
-        <v>6739.8000000000038</v>
+        <v>6633.9600000000046</v>
       </c>
       <c r="P28" s="6">
         <f t="shared" si="13"/>
@@ -8812,7 +8795,7 @@
       </c>
       <c r="Q28" s="6">
         <f t="shared" si="14"/>
-        <v>-67.663333333333327</v>
+        <v>-66.566000000000003</v>
       </c>
       <c r="R28" s="6">
         <f t="shared" si="29"/>
@@ -8820,7 +8803,7 @@
       </c>
       <c r="S28" s="6">
         <f t="shared" ref="S28" si="102">Q28</f>
-        <v>-67.663333333333327</v>
+        <v>-66.566000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8833,14 +8816,14 @@
       </c>
       <c r="C29" s="6">
         <f>C28+B6</f>
-        <v>6720.7999999999984</v>
+        <v>6643.4181818181742</v>
       </c>
       <c r="D29" s="6">
         <v>4314</v>
       </c>
       <c r="E29" s="6">
         <f t="shared" si="24"/>
-        <v>6720.7999999999984</v>
+        <v>6643.4181818181742</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="25"/>
@@ -8848,7 +8831,7 @@
       </c>
       <c r="G29" s="6">
         <f t="shared" si="26"/>
-        <v>-67.346666666666664</v>
+        <v>-66.72363636363616</v>
       </c>
       <c r="H29" s="6">
         <f t="shared" si="35"/>
@@ -8856,7 +8839,7 @@
       </c>
       <c r="I29" s="6">
         <f t="shared" ref="I29" si="103">G29</f>
-        <v>-67.346666666666664</v>
+        <v>-66.72363636363616</v>
       </c>
       <c r="K29" s="6">
         <f t="shared" si="28"/>
@@ -8867,14 +8850,14 @@
       </c>
       <c r="M29" s="6">
         <f>M28+L5</f>
-        <v>6746.100000000004</v>
+        <v>6635.2200000000048</v>
       </c>
       <c r="N29" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O29" s="6">
         <f t="shared" si="12"/>
-        <v>6746.100000000004</v>
+        <v>6635.2200000000048</v>
       </c>
       <c r="P29" s="6">
         <f t="shared" si="13"/>
@@ -8882,7 +8865,7 @@
       </c>
       <c r="Q29" s="6">
         <f t="shared" si="14"/>
-        <v>-67.768333333333331</v>
+        <v>-66.587000000000003</v>
       </c>
       <c r="R29" s="6">
         <f t="shared" si="29"/>
@@ -8890,7 +8873,7 @@
       </c>
       <c r="S29" s="6">
         <f t="shared" ref="S29" si="104">Q29</f>
-        <v>-67.768333333333331</v>
+        <v>-66.587000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8903,14 +8886,14 @@
       </c>
       <c r="C30" s="6">
         <f>C29+B6</f>
-        <v>6725.866666666665</v>
+        <v>6644.799999999992</v>
       </c>
       <c r="D30" s="6">
         <v>4314</v>
       </c>
       <c r="E30" s="6">
         <f t="shared" si="24"/>
-        <v>6725.866666666665</v>
+        <v>6644.799999999992</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" si="25"/>
@@ -8918,7 +8901,7 @@
       </c>
       <c r="G30" s="6">
         <f t="shared" si="26"/>
-        <v>-67.431111111110994</v>
+        <v>-66.746666666666499</v>
       </c>
       <c r="H30" s="6">
         <f t="shared" si="35"/>
@@ -8926,7 +8909,7 @@
       </c>
       <c r="I30" s="6">
         <f t="shared" ref="I30" si="105">G30</f>
-        <v>-67.431111111110994</v>
+        <v>-66.746666666666499</v>
       </c>
       <c r="K30" s="6">
         <f t="shared" si="28"/>
@@ -8937,14 +8920,14 @@
       </c>
       <c r="M30" s="6">
         <f>M29+L5</f>
-        <v>6752.4000000000042</v>
+        <v>6636.480000000005</v>
       </c>
       <c r="N30" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O30" s="6">
         <f t="shared" si="12"/>
-        <v>6752.4000000000042</v>
+        <v>6636.480000000005</v>
       </c>
       <c r="P30" s="6">
         <f t="shared" si="13"/>
@@ -8952,7 +8935,7 @@
       </c>
       <c r="Q30" s="6">
         <f t="shared" si="14"/>
-        <v>-67.873333333333335</v>
+        <v>-66.60800000000016</v>
       </c>
       <c r="R30" s="6">
         <f t="shared" si="29"/>
@@ -8960,7 +8943,7 @@
       </c>
       <c r="S30" s="6">
         <f t="shared" ref="S30" si="106">Q30</f>
-        <v>-67.873333333333335</v>
+        <v>-66.60800000000016</v>
       </c>
     </row>
     <row r="31" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8973,14 +8956,14 @@
       </c>
       <c r="C31" s="6">
         <f>C30+B6</f>
-        <v>6730.9333333333316</v>
+        <v>6646.1818181818098</v>
       </c>
       <c r="D31" s="6">
         <v>4314</v>
       </c>
       <c r="E31" s="6">
         <f t="shared" si="24"/>
-        <v>6730.9333333333316</v>
+        <v>6646.1818181818098</v>
       </c>
       <c r="F31" s="6">
         <f t="shared" si="25"/>
@@ -8988,7 +8971,7 @@
       </c>
       <c r="G31" s="6">
         <f t="shared" si="26"/>
-        <v>-67.515555555555494</v>
+        <v>-66.769696969696838</v>
       </c>
       <c r="H31" s="6">
         <f t="shared" si="35"/>
@@ -8996,7 +8979,7 @@
       </c>
       <c r="I31" s="6">
         <f t="shared" ref="I31" si="107">G31</f>
-        <v>-67.515555555555494</v>
+        <v>-66.769696969696838</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>30</v>

--- a/Surveys/Survey Lines/Survey Lines.xlsx
+++ b/Surveys/Survey Lines/Survey Lines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/Survey Lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{EE423639-233B-4791-B77F-F82BF1D43694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE12C29-40AF-4AE5-BFD0-3A76CB22B02D}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{EE423639-233B-4791-B77F-F82BF1D43694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91A680F6-5C21-48BB-A82F-67871C5C5168}"/>
   <bookViews>
-    <workbookView xWindow="-35390" yWindow="1490" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-20" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Entry" sheetId="1" r:id="rId1"/>
@@ -401,6 +401,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -623,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -959,49 +963,49 @@
         <v>4334</v>
       </c>
       <c r="C12" s="16">
-        <v>6615.7818181818175</v>
+        <v>6615.413333333333</v>
       </c>
       <c r="D12" s="16">
         <v>4314</v>
       </c>
       <c r="E12" s="16">
-        <v>6615.7818181818175</v>
+        <v>6615.413333333333</v>
       </c>
       <c r="F12" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G12" s="12">
-        <v>-66.263030303030334</v>
+        <v>-66.256888888888838</v>
       </c>
       <c r="H12" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I12" s="12">
-        <v>-66.263030303030334</v>
+        <v>-66.256888888888838</v>
       </c>
       <c r="L12" s="6">
         <v>4330.12</v>
       </c>
       <c r="M12" s="6">
-        <v>6608.76</v>
+        <v>6608.4</v>
       </c>
       <c r="N12" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O12" s="6">
-        <v>6608.76</v>
+        <v>6608.4</v>
       </c>
       <c r="P12" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q12" s="6">
-        <v>-66.146000000000001</v>
+        <v>-66.14</v>
       </c>
       <c r="R12" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S12" s="6">
-        <v>-66.146000000000001</v>
+        <v>-66.14</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -1015,49 +1019,49 @@
         <v>4334</v>
       </c>
       <c r="C13" s="16">
-        <v>6617.1636363636353</v>
+        <v>6616.4266666666663</v>
       </c>
       <c r="D13" s="16">
         <v>4314</v>
       </c>
       <c r="E13" s="16">
-        <v>6617.1636363636353</v>
+        <v>6616.4266666666663</v>
       </c>
       <c r="F13" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G13" s="12">
-        <v>-66.286060606060673</v>
+        <v>-66.273777777777838</v>
       </c>
       <c r="H13" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I13" s="12">
-        <v>-66.286060606060673</v>
+        <v>-66.273777777777838</v>
       </c>
       <c r="L13" s="6">
         <v>4330.12</v>
       </c>
       <c r="M13" s="6">
-        <v>6610.02</v>
+        <v>6609.2999999999993</v>
       </c>
       <c r="N13" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O13" s="6">
-        <v>6610.02</v>
+        <v>6609.2999999999993</v>
       </c>
       <c r="P13" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q13" s="6">
-        <v>-66.167000000000002</v>
+        <v>-66.155000000000001</v>
       </c>
       <c r="R13" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S13" s="6">
-        <v>-66.167000000000002</v>
+        <v>-66.155000000000001</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -1071,49 +1075,49 @@
         <v>4334</v>
       </c>
       <c r="C14" s="16">
-        <v>6618.5454545454531</v>
+        <v>6617.44</v>
       </c>
       <c r="D14" s="16">
         <v>4314</v>
       </c>
       <c r="E14" s="16">
-        <v>6618.5454545454531</v>
+        <v>6617.44</v>
       </c>
       <c r="F14" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G14" s="12">
-        <v>-66.309090909090827</v>
+        <v>-66.290666666666667</v>
       </c>
       <c r="H14" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I14" s="12">
-        <v>-66.309090909090827</v>
+        <v>-66.290666666666667</v>
       </c>
       <c r="L14" s="6">
         <v>4330.12</v>
       </c>
       <c r="M14" s="6">
-        <v>6611.2800000000007</v>
+        <v>6610.1999999999989</v>
       </c>
       <c r="N14" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O14" s="6">
-        <v>6611.2800000000007</v>
+        <v>6610.1999999999989</v>
       </c>
       <c r="P14" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q14" s="6">
-        <v>-66.188000000000002</v>
+        <v>-66.17</v>
       </c>
       <c r="R14" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S14" s="6">
-        <v>-66.188000000000002</v>
+        <v>-66.17</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -1127,49 +1131,49 @@
         <v>4334</v>
       </c>
       <c r="C15" s="16">
-        <v>6619.927272727271</v>
+        <v>6618.4533333333329</v>
       </c>
       <c r="D15" s="16">
         <v>4314</v>
       </c>
       <c r="E15" s="16">
-        <v>6619.927272727271</v>
+        <v>6618.4533333333329</v>
       </c>
       <c r="F15" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G15" s="12">
-        <v>-66.332121212121166</v>
+        <v>-66.307555555555496</v>
       </c>
       <c r="H15" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I15" s="12">
-        <v>-66.332121212121166</v>
+        <v>-66.307555555555496</v>
       </c>
       <c r="L15" s="6">
         <v>4330.12</v>
       </c>
       <c r="M15" s="6">
-        <v>6612.5400000000009</v>
+        <v>6611.0999999999985</v>
       </c>
       <c r="N15" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O15" s="6">
-        <v>6612.5400000000009</v>
+        <v>6611.0999999999985</v>
       </c>
       <c r="P15" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q15" s="6">
-        <v>-66.209000000000003</v>
+        <v>-66.185000000000002</v>
       </c>
       <c r="R15" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S15" s="6">
-        <v>-66.209000000000003</v>
+        <v>-66.185000000000002</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -1183,49 +1187,49 @@
         <v>4334</v>
       </c>
       <c r="C16" s="16">
-        <v>6621.3090909090888</v>
+        <v>6619.4666666666662</v>
       </c>
       <c r="D16" s="16">
         <v>4314</v>
       </c>
       <c r="E16" s="16">
-        <v>6621.3090909090888</v>
+        <v>6619.4666666666662</v>
       </c>
       <c r="F16" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G16" s="12">
-        <v>-66.355151515151505</v>
+        <v>-66.324444444444495</v>
       </c>
       <c r="H16" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I16" s="12">
-        <v>-66.355151515151505</v>
+        <v>-66.324444444444495</v>
       </c>
       <c r="L16" s="6">
         <v>4330.12</v>
       </c>
       <c r="M16" s="6">
-        <v>6613.8000000000011</v>
+        <v>6611.9999999999982</v>
       </c>
       <c r="N16" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O16" s="6">
-        <v>6613.8000000000011</v>
+        <v>6611.9999999999982</v>
       </c>
       <c r="P16" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q16" s="6">
-        <v>-66.23</v>
+        <v>-66.2</v>
       </c>
       <c r="R16" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S16" s="6">
-        <v>-66.23</v>
+        <v>-66.2</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -1239,50 +1243,50 @@
         <v>4334</v>
       </c>
       <c r="C17" s="16">
-        <v>6622.6909090909066</v>
+        <v>6620.48</v>
       </c>
       <c r="D17" s="16">
         <v>4314</v>
       </c>
       <c r="E17" s="16">
-        <v>6622.6909090909066</v>
+        <v>6620.48</v>
       </c>
       <c r="F17" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G17" s="12">
-        <v>-66.378181818181829</v>
+        <v>-66.341333333333338</v>
       </c>
       <c r="H17" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I17" s="12">
-        <v>-66.378181818181829</v>
+        <v>-66.341333333333338</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="6">
         <v>4330.12</v>
       </c>
       <c r="M17" s="6">
-        <v>6615.0600000000013</v>
+        <v>6612.8999999999978</v>
       </c>
       <c r="N17" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O17" s="6">
-        <v>6615.0600000000013</v>
+        <v>6612.8999999999978</v>
       </c>
       <c r="P17" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q17" s="6">
-        <v>-66.251000000000005</v>
+        <v>-66.215000000000003</v>
       </c>
       <c r="R17" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S17" s="6">
-        <v>-66.251000000000005</v>
+        <v>-66.215000000000003</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -1296,50 +1300,50 @@
         <v>4334</v>
       </c>
       <c r="C18" s="16">
-        <v>6624.0727272727245</v>
+        <v>6621.4933333333329</v>
       </c>
       <c r="D18" s="16">
         <v>4314</v>
       </c>
       <c r="E18" s="16">
-        <v>6624.0727272727245</v>
+        <v>6621.4933333333329</v>
       </c>
       <c r="F18" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G18" s="12">
-        <v>-66.401212121211998</v>
+        <v>-66.358222222222167</v>
       </c>
       <c r="H18" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I18" s="12">
-        <v>-66.401212121211998</v>
+        <v>-66.358222222222167</v>
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="6">
         <v>4330.12</v>
       </c>
       <c r="M18" s="6">
-        <v>6616.3200000000015</v>
+        <v>6613.7999999999975</v>
       </c>
       <c r="N18" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O18" s="6">
-        <v>6616.3200000000015</v>
+        <v>6613.7999999999975</v>
       </c>
       <c r="P18" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q18" s="6">
-        <v>-66.272000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="R18" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S18" s="6">
-        <v>-66.272000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -1353,49 +1357,49 @@
         <v>4334</v>
       </c>
       <c r="C19" s="16">
-        <v>6625.4545454545423</v>
+        <v>6622.5066666666662</v>
       </c>
       <c r="D19" s="16">
         <v>4314</v>
       </c>
       <c r="E19" s="16">
-        <v>6625.4545454545423</v>
+        <v>6622.5066666666662</v>
       </c>
       <c r="F19" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G19" s="12">
-        <v>-66.424242424242337</v>
+        <v>-66.375111111111167</v>
       </c>
       <c r="H19" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I19" s="12">
-        <v>-66.424242424242337</v>
+        <v>-66.375111111111167</v>
       </c>
       <c r="L19" s="6">
         <v>4330.12</v>
       </c>
       <c r="M19" s="6">
-        <v>6617.5800000000017</v>
+        <v>6614.6999999999971</v>
       </c>
       <c r="N19" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O19" s="6">
-        <v>6617.5800000000017</v>
+        <v>6614.6999999999971</v>
       </c>
       <c r="P19" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q19" s="6">
-        <v>-66.293000000000006</v>
+        <v>-66.245000000000005</v>
       </c>
       <c r="R19" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S19" s="6">
-        <v>-66.293000000000006</v>
+        <v>-66.245000000000005</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -1409,49 +1413,49 @@
         <v>4334</v>
       </c>
       <c r="C20" s="16">
-        <v>6626.8363636363601</v>
+        <v>6623.5199999999995</v>
       </c>
       <c r="D20" s="16">
         <v>4314</v>
       </c>
       <c r="E20" s="16">
-        <v>6626.8363636363601</v>
+        <v>6623.5199999999995</v>
       </c>
       <c r="F20" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G20" s="12">
-        <v>-66.447272727272662</v>
+        <v>-66.391999999999996</v>
       </c>
       <c r="H20" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I20" s="12">
-        <v>-66.447272727272662</v>
+        <v>-66.391999999999996</v>
       </c>
       <c r="L20" s="6">
         <v>4330.12</v>
       </c>
       <c r="M20" s="6">
-        <v>6618.840000000002</v>
+        <v>6615.5999999999967</v>
       </c>
       <c r="N20" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O20" s="6">
-        <v>6618.840000000002</v>
+        <v>6615.5999999999967</v>
       </c>
       <c r="P20" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q20" s="6">
-        <v>-66.313999999999993</v>
+        <v>-66.260000000000005</v>
       </c>
       <c r="R20" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S20" s="6">
-        <v>-66.313999999999993</v>
+        <v>-66.260000000000005</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -1465,49 +1469,49 @@
         <v>4334</v>
       </c>
       <c r="C21" s="16">
-        <v>6628.218181818178</v>
+        <v>6624.5333333333328</v>
       </c>
       <c r="D21" s="16">
         <v>4314</v>
       </c>
       <c r="E21" s="16">
-        <v>6628.218181818178</v>
+        <v>6624.5333333333328</v>
       </c>
       <c r="F21" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G21" s="12">
-        <v>-66.470303030303</v>
+        <v>-66.408888888888839</v>
       </c>
       <c r="H21" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I21" s="12">
-        <v>-66.470303030303</v>
+        <v>-66.408888888888839</v>
       </c>
       <c r="L21" s="6">
         <v>4330.12</v>
       </c>
       <c r="M21" s="6">
-        <v>6620.1000000000022</v>
+        <v>6616.4999999999964</v>
       </c>
       <c r="N21" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O21" s="6">
-        <v>6620.1000000000022</v>
+        <v>6616.4999999999964</v>
       </c>
       <c r="P21" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q21" s="6">
-        <v>-66.334999999999994</v>
+        <v>-66.275000000000006</v>
       </c>
       <c r="R21" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S21" s="6">
-        <v>-66.334999999999994</v>
+        <v>-66.275000000000006</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -1521,49 +1525,49 @@
         <v>4334</v>
       </c>
       <c r="C22" s="16">
-        <v>6629.5999999999958</v>
+        <v>6625.5466666666662</v>
       </c>
       <c r="D22" s="16">
         <v>4314</v>
       </c>
       <c r="E22" s="16">
-        <v>6629.5999999999958</v>
+        <v>6625.5466666666662</v>
       </c>
       <c r="F22" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G22" s="12">
-        <v>-66.493333333333339</v>
+        <v>-66.425777777777839</v>
       </c>
       <c r="H22" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I22" s="12">
-        <v>-66.493333333333339</v>
+        <v>-66.425777777777839</v>
       </c>
       <c r="L22" s="6">
         <v>4330.12</v>
       </c>
       <c r="M22" s="6">
-        <v>6621.3600000000024</v>
+        <v>6617.399999999996</v>
       </c>
       <c r="N22" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O22" s="6">
-        <v>6621.3600000000024</v>
+        <v>6617.399999999996</v>
       </c>
       <c r="P22" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q22" s="6">
-        <v>-66.355999999999995</v>
+        <v>-66.290000000000006</v>
       </c>
       <c r="R22" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S22" s="6">
-        <v>-66.355999999999995</v>
+        <v>-66.290000000000006</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -1577,49 +1581,49 @@
         <v>4334</v>
       </c>
       <c r="C23" s="16">
-        <v>6630.9818181818137</v>
+        <v>6626.5599999999995</v>
       </c>
       <c r="D23" s="16">
         <v>4314</v>
       </c>
       <c r="E23" s="16">
-        <v>6630.9818181818137</v>
+        <v>6626.5599999999995</v>
       </c>
       <c r="F23" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G23" s="12">
-        <v>-66.516363636363494</v>
+        <v>-66.442666666666668</v>
       </c>
       <c r="H23" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I23" s="12">
-        <v>-66.516363636363494</v>
+        <v>-66.442666666666668</v>
       </c>
       <c r="L23" s="6">
         <v>4330.12</v>
       </c>
       <c r="M23" s="6">
-        <v>6622.6200000000026</v>
+        <v>6618.2999999999956</v>
       </c>
       <c r="N23" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O23" s="6">
-        <v>6622.6200000000026</v>
+        <v>6618.2999999999956</v>
       </c>
       <c r="P23" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q23" s="6">
-        <v>-66.376999999999995</v>
+        <v>-66.305000000000007</v>
       </c>
       <c r="R23" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S23" s="6">
-        <v>-66.376999999999995</v>
+        <v>-66.305000000000007</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -1633,49 +1637,49 @@
         <v>4334</v>
       </c>
       <c r="C24" s="16">
-        <v>6632.3636363636315</v>
+        <v>6627.5733333333328</v>
       </c>
       <c r="D24" s="16">
         <v>4314</v>
       </c>
       <c r="E24" s="16">
-        <v>6632.3636363636315</v>
+        <v>6627.5733333333328</v>
       </c>
       <c r="F24" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G24" s="12">
-        <v>-66.539393939393833</v>
+        <v>-66.459555555555497</v>
       </c>
       <c r="H24" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I24" s="12">
-        <v>-66.539393939393833</v>
+        <v>-66.459555555555497</v>
       </c>
       <c r="L24" s="6">
         <v>4330.12</v>
       </c>
       <c r="M24" s="6">
-        <v>6623.8800000000028</v>
+        <v>6619.1999999999953</v>
       </c>
       <c r="N24" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O24" s="6">
-        <v>6623.8800000000028</v>
+        <v>6619.1999999999953</v>
       </c>
       <c r="P24" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q24" s="6">
-        <v>-66.397999999999996</v>
+        <v>-66.319999999999993</v>
       </c>
       <c r="R24" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S24" s="6">
-        <v>-66.397999999999996</v>
+        <v>-66.319999999999993</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -1689,49 +1693,49 @@
         <v>4334</v>
       </c>
       <c r="C25" s="16">
-        <v>6633.7454545454493</v>
+        <v>6628.5866666666661</v>
       </c>
       <c r="D25" s="16">
         <v>4314</v>
       </c>
       <c r="E25" s="16">
-        <v>6633.7454545454493</v>
+        <v>6628.5866666666661</v>
       </c>
       <c r="F25" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G25" s="12">
-        <v>-66.562424242424171</v>
+        <v>-66.476444444444496</v>
       </c>
       <c r="H25" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I25" s="12">
-        <v>-66.562424242424171</v>
+        <v>-66.476444444444496</v>
       </c>
       <c r="L25" s="6">
         <v>4330.12</v>
       </c>
       <c r="M25" s="6">
-        <v>6625.1400000000031</v>
+        <v>6620.0999999999949</v>
       </c>
       <c r="N25" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O25" s="6">
-        <v>6625.1400000000031</v>
+        <v>6620.0999999999949</v>
       </c>
       <c r="P25" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q25" s="6">
-        <v>-66.418999999999997</v>
+        <v>-66.334999999999837</v>
       </c>
       <c r="R25" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S25" s="6">
-        <v>-66.418999999999997</v>
+        <v>-66.334999999999837</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -1745,49 +1749,49 @@
         <v>4334</v>
       </c>
       <c r="C26" s="16">
-        <v>6635.1272727272672</v>
+        <v>6629.5999999999995</v>
       </c>
       <c r="D26" s="16">
         <v>4314</v>
       </c>
       <c r="E26" s="16">
-        <v>6635.1272727272672</v>
+        <v>6629.5999999999995</v>
       </c>
       <c r="F26" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G26" s="12">
-        <v>-66.585454545454496</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="H26" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I26" s="12">
-        <v>-66.585454545454496</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="L26" s="6">
         <v>4330.12</v>
       </c>
       <c r="M26" s="6">
-        <v>6626.4000000000033</v>
+        <v>6620.9999999999945</v>
       </c>
       <c r="N26" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O26" s="6">
-        <v>6626.4000000000033</v>
+        <v>6620.9999999999945</v>
       </c>
       <c r="P26" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q26" s="6">
-        <v>-66.44</v>
+        <v>-66.349999999999838</v>
       </c>
       <c r="R26" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S26" s="6">
-        <v>-66.44</v>
+        <v>-66.349999999999838</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -1801,49 +1805,49 @@
         <v>4334</v>
       </c>
       <c r="C27" s="16">
-        <v>6636.509090909085</v>
+        <v>6630.6133333333328</v>
       </c>
       <c r="D27" s="16">
         <v>4314</v>
       </c>
       <c r="E27" s="16">
-        <v>6636.509090909085</v>
+        <v>6630.6133333333328</v>
       </c>
       <c r="F27" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G27" s="12">
-        <v>-66.608484848484665</v>
+        <v>-66.510222222222168</v>
       </c>
       <c r="H27" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I27" s="12">
-        <v>-66.608484848484665</v>
+        <v>-66.510222222222168</v>
       </c>
       <c r="L27" s="6">
         <v>4330.12</v>
       </c>
       <c r="M27" s="6">
-        <v>6627.6600000000035</v>
+        <v>6621.8999999999942</v>
       </c>
       <c r="N27" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O27" s="6">
-        <v>6627.6600000000035</v>
+        <v>6621.8999999999942</v>
       </c>
       <c r="P27" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q27" s="6">
-        <v>-66.460999999999999</v>
+        <v>-66.364999999999839</v>
       </c>
       <c r="R27" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S27" s="6">
-        <v>-66.460999999999999</v>
+        <v>-66.364999999999839</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -1857,49 +1861,49 @@
         <v>4334</v>
       </c>
       <c r="C28" s="16">
-        <v>6637.8909090909028</v>
+        <v>6631.6266666666661</v>
       </c>
       <c r="D28" s="16">
         <v>4314</v>
       </c>
       <c r="E28" s="16">
-        <v>6637.8909090909028</v>
+        <v>6631.6266666666661</v>
       </c>
       <c r="F28" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G28" s="12">
-        <v>-66.631515151515003</v>
+        <v>-66.527111111111168</v>
       </c>
       <c r="H28" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I28" s="12">
-        <v>-66.631515151515003</v>
+        <v>-66.527111111111168</v>
       </c>
       <c r="L28" s="6">
         <v>4330.12</v>
       </c>
       <c r="M28" s="6">
-        <v>6628.9200000000037</v>
+        <v>6622.7999999999938</v>
       </c>
       <c r="N28" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O28" s="6">
-        <v>6628.9200000000037</v>
+        <v>6622.7999999999938</v>
       </c>
       <c r="P28" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q28" s="6">
-        <v>-66.481999999999999</v>
+        <v>-66.379999999999839</v>
       </c>
       <c r="R28" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S28" s="6">
-        <v>-66.481999999999999</v>
+        <v>-66.379999999999839</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -1913,49 +1917,49 @@
         <v>4334</v>
       </c>
       <c r="C29" s="16">
-        <v>6639.2727272727207</v>
+        <v>6632.6399999999994</v>
       </c>
       <c r="D29" s="16">
         <v>4314</v>
       </c>
       <c r="E29" s="16">
-        <v>6639.2727272727207</v>
+        <v>6632.6399999999994</v>
       </c>
       <c r="F29" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G29" s="12">
-        <v>-66.654545454545328</v>
+        <v>-66.543999999999997</v>
       </c>
       <c r="H29" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I29" s="12">
-        <v>-66.654545454545328</v>
+        <v>-66.543999999999997</v>
       </c>
       <c r="L29" s="6">
         <v>4330.12</v>
       </c>
       <c r="M29" s="6">
-        <v>6630.1800000000039</v>
+        <v>6623.6999999999935</v>
       </c>
       <c r="N29" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O29" s="6">
-        <v>6630.1800000000039</v>
+        <v>6623.6999999999935</v>
       </c>
       <c r="P29" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q29" s="6">
-        <v>-66.503</v>
+        <v>-66.39499999999984</v>
       </c>
       <c r="R29" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S29" s="6">
-        <v>-66.503</v>
+        <v>-66.39499999999984</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -1969,49 +1973,49 @@
         <v>4334</v>
       </c>
       <c r="C30" s="16">
-        <v>6640.6545454545385</v>
+        <v>6633.6533333333327</v>
       </c>
       <c r="D30" s="16">
         <v>4314</v>
       </c>
       <c r="E30" s="16">
-        <v>6640.6545454545385</v>
+        <v>6633.6533333333327</v>
       </c>
       <c r="F30" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G30" s="12">
-        <v>-66.677575757575667</v>
+        <v>-66.56088888888884</v>
       </c>
       <c r="H30" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I30" s="12">
-        <v>-66.677575757575667</v>
+        <v>-66.56088888888884</v>
       </c>
       <c r="L30" s="6">
         <v>4330.12</v>
       </c>
       <c r="M30" s="6">
-        <v>6631.4400000000041</v>
+        <v>6624.5999999999931</v>
       </c>
       <c r="N30" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O30" s="6">
-        <v>6631.4400000000041</v>
+        <v>6624.5999999999931</v>
       </c>
       <c r="P30" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q30" s="6">
-        <v>-66.524000000000001</v>
+        <v>-66.40999999999984</v>
       </c>
       <c r="R30" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S30" s="6">
-        <v>-66.524000000000001</v>
+        <v>-66.40999999999984</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -2025,49 +2029,49 @@
         <v>4334</v>
       </c>
       <c r="C31" s="16">
-        <v>6642.0363636363563</v>
+        <v>6634.6666666666661</v>
       </c>
       <c r="D31" s="16">
         <v>4314</v>
       </c>
       <c r="E31" s="16">
-        <v>6642.0363636363563</v>
+        <v>6634.6666666666661</v>
       </c>
       <c r="F31" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G31" s="12">
-        <v>-66.700606060606006</v>
+        <v>-66.57777777777784</v>
       </c>
       <c r="H31" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I31" s="12">
-        <v>-66.700606060606006</v>
+        <v>-66.57777777777784</v>
       </c>
       <c r="L31" s="6">
         <v>4330.12</v>
       </c>
       <c r="M31" s="6">
-        <v>6632.7000000000044</v>
+        <v>6625.4999999999927</v>
       </c>
       <c r="N31" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O31" s="6">
-        <v>6632.7000000000044</v>
+        <v>6625.4999999999927</v>
       </c>
       <c r="P31" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q31" s="6">
-        <v>-66.545000000000002</v>
+        <v>-66.424999999999827</v>
       </c>
       <c r="R31" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S31" s="6">
-        <v>-66.545000000000002</v>
+        <v>-66.424999999999827</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -2081,49 +2085,49 @@
         <v>4334</v>
       </c>
       <c r="C32" s="16">
-        <v>6643.4181818181742</v>
+        <v>6635.6799999999994</v>
       </c>
       <c r="D32" s="16">
         <v>4314</v>
       </c>
       <c r="E32" s="16">
-        <v>6643.4181818181742</v>
+        <v>6635.6799999999994</v>
       </c>
       <c r="F32" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G32" s="12">
-        <v>-66.72363636363616</v>
+        <v>-66.594666666666669</v>
       </c>
       <c r="H32" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I32" s="12">
-        <v>-66.72363636363616</v>
+        <v>-66.594666666666669</v>
       </c>
       <c r="L32" s="6">
         <v>4330.12</v>
       </c>
       <c r="M32" s="6">
-        <v>6633.9600000000046</v>
+        <v>6626.3999999999924</v>
       </c>
       <c r="N32" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O32" s="6">
-        <v>6633.9600000000046</v>
+        <v>6626.3999999999924</v>
       </c>
       <c r="P32" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q32" s="6">
-        <v>-66.566000000000003</v>
+        <v>-66.439999999999827</v>
       </c>
       <c r="R32" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S32" s="6">
-        <v>-66.566000000000003</v>
+        <v>-66.439999999999827</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -2137,49 +2141,49 @@
         <v>4334</v>
       </c>
       <c r="C33" s="16">
-        <v>6644.799999999992</v>
+        <v>6636.6933333333327</v>
       </c>
       <c r="D33" s="16">
         <v>4314</v>
       </c>
       <c r="E33" s="16">
-        <v>6644.799999999992</v>
+        <v>6636.6933333333327</v>
       </c>
       <c r="F33" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G33" s="12">
-        <v>-66.746666666666499</v>
+        <v>-66.611555555555498</v>
       </c>
       <c r="H33" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I33" s="12">
-        <v>-66.746666666666499</v>
+        <v>-66.611555555555498</v>
       </c>
       <c r="L33" s="6">
         <v>4330.12</v>
       </c>
       <c r="M33" s="6">
-        <v>6635.2200000000048</v>
+        <v>6627.299999999992</v>
       </c>
       <c r="N33" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O33" s="6">
-        <v>6635.2200000000048</v>
+        <v>6627.299999999992</v>
       </c>
       <c r="P33" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q33" s="6">
-        <v>-66.587000000000003</v>
+        <v>-66.454999999999828</v>
       </c>
       <c r="R33" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S33" s="6">
-        <v>-66.587000000000003</v>
+        <v>-66.454999999999828</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -2193,49 +2197,49 @@
         <v>4334</v>
       </c>
       <c r="C34" s="16">
-        <v>6646.1818181818098</v>
+        <v>6637.706666666666</v>
       </c>
       <c r="D34" s="16">
         <v>4314</v>
       </c>
       <c r="E34" s="16">
-        <v>6646.1818181818098</v>
+        <v>6637.706666666666</v>
       </c>
       <c r="F34" s="12">
         <v>43.56666666666667</v>
       </c>
       <c r="G34" s="12">
-        <v>-66.769696969696838</v>
+        <v>-66.628444444444497</v>
       </c>
       <c r="H34" s="12">
         <v>43.233333333333334</v>
       </c>
       <c r="I34" s="12">
-        <v>-66.769696969696838</v>
+        <v>-66.628444444444497</v>
       </c>
       <c r="L34" s="6">
         <v>4330.12</v>
       </c>
       <c r="M34" s="6">
-        <v>6636.480000000005</v>
+        <v>6628.1999999999916</v>
       </c>
       <c r="N34" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O34" s="6">
-        <v>6636.480000000005</v>
+        <v>6628.1999999999916</v>
       </c>
       <c r="P34" s="6">
         <v>43.502000000000002</v>
       </c>
       <c r="Q34" s="6">
-        <v>-66.60800000000016</v>
+        <v>-66.469999999999828</v>
       </c>
       <c r="R34" s="6">
         <v>43.247500000000002</v>
       </c>
       <c r="S34" s="6">
-        <v>-66.60800000000016</v>
+        <v>-66.469999999999828</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -5997,11 +6001,11 @@
       </c>
       <c r="V3" s="8">
         <f>B4</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X3" s="6">
         <f t="shared" ref="X3:X4" si="8">V3</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE3" s="6" t="s">
         <v>23</v>
@@ -6028,7 +6032,7 @@
       </c>
       <c r="B4" s="8">
         <f>'Data Entry'!B1</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -6043,7 +6047,7 @@
       </c>
       <c r="L4" s="8">
         <f>B4</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -6055,15 +6059,15 @@
       </c>
       <c r="V4" s="6">
         <f>V3*2</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X4" s="6">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y4" s="6">
         <f>X4</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>24</v>
@@ -6091,7 +6095,7 @@
       </c>
       <c r="B5" s="6">
         <f>B4*2</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -6103,7 +6107,7 @@
       </c>
       <c r="L5" s="6">
         <f>(L31-L3)/(L4-1)</f>
-        <v>1.2600000000000364</v>
+        <v>0.900000000000026</v>
       </c>
       <c r="P5" s="8" t="s">
         <v>26</v>
@@ -6113,15 +6117,15 @@
       </c>
       <c r="V5" s="6">
         <f>(V2-V25)/(V4-1)</f>
-        <v>0.71072727272729186</v>
+        <v>0.5212000000000141</v>
       </c>
       <c r="X5" s="6">
         <f t="shared" ref="X5:Y5" si="10">(X2-X25)/(X4-1)</f>
-        <v>0.52063636363635102</v>
+        <v>0.38179999999999076</v>
       </c>
       <c r="Y5" s="6">
         <f t="shared" si="10"/>
-        <v>0.78509090909094748</v>
+        <v>0.57573333333336152</v>
       </c>
       <c r="Z5" s="8" t="s">
         <v>26</v>
@@ -6151,7 +6155,7 @@
       </c>
       <c r="B6" s="6">
         <f>(B32-B3)/(B5-1)</f>
-        <v>1.381818181818248</v>
+        <v>1.0133333333333818</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>26</v>
@@ -6357,14 +6361,14 @@
       </c>
       <c r="M8" s="6">
         <f>M7+L5</f>
-        <v>6608.76</v>
+        <v>6608.4</v>
       </c>
       <c r="N8" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O8" s="6">
         <f t="shared" si="12"/>
-        <v>6608.76</v>
+        <v>6608.4</v>
       </c>
       <c r="P8" s="6">
         <f t="shared" si="13"/>
@@ -6372,7 +6376,7 @@
       </c>
       <c r="Q8" s="6">
         <f t="shared" si="14"/>
-        <v>-66.146000000000001</v>
+        <v>-66.14</v>
       </c>
       <c r="R8" s="6">
         <f t="shared" ref="R8:R30" si="29">(LEFT(N8,2)+((RIGHT(N8,LEN(N8)-2))/60))</f>
@@ -6380,7 +6384,7 @@
       </c>
       <c r="S8" s="6">
         <f t="shared" ref="S8" si="30">Q8</f>
-        <v>-66.146000000000001</v>
+        <v>-66.14</v>
       </c>
       <c r="U8" s="6">
         <f t="shared" ref="U8:U24" si="31">U7+1</f>
@@ -6388,22 +6392,22 @@
       </c>
       <c r="V8" s="6">
         <f>V7+$V5</f>
-        <v>4502.8927272727269</v>
+        <v>4502.7031999999999</v>
       </c>
       <c r="W8" s="6">
         <v>6514</v>
       </c>
       <c r="X8" s="6">
         <f t="shared" ref="X8:Y8" si="32">X7+X5</f>
-        <v>4513.4936363636361</v>
+        <v>4513.3548000000001</v>
       </c>
       <c r="Y8" s="6">
         <f t="shared" si="32"/>
-        <v>6441.6490909090908</v>
+        <v>6441.4397333333327</v>
       </c>
       <c r="Z8" s="6">
         <f t="shared" si="16"/>
-        <v>45.048212121212167</v>
+        <v>45.045053333333335</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="17"/>
@@ -6411,11 +6415,11 @@
       </c>
       <c r="AB8" s="6">
         <f t="shared" si="18"/>
-        <v>45.224893939394001</v>
+        <v>45.222580000000001</v>
       </c>
       <c r="AC8" s="6">
         <f t="shared" si="19"/>
-        <v>-64.694151515151503</v>
+        <v>-64.690662222222173</v>
       </c>
       <c r="AE8" s="6">
         <v>2</v>
@@ -6462,14 +6466,14 @@
       </c>
       <c r="C9" s="6">
         <f>C8+B6</f>
-        <v>6615.7818181818175</v>
+        <v>6615.413333333333</v>
       </c>
       <c r="D9" s="6">
         <v>4314</v>
       </c>
       <c r="E9" s="6">
         <f t="shared" si="24"/>
-        <v>6615.7818181818175</v>
+        <v>6615.413333333333</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="25"/>
@@ -6477,7 +6481,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="26"/>
-        <v>-66.263030303030334</v>
+        <v>-66.256888888888838</v>
       </c>
       <c r="H9" s="6">
         <f t="shared" ref="H9:H31" si="35">(LEFT(D9,2)+((RIGHT(D9,LEN(D9)-2))/60))</f>
@@ -6485,7 +6489,7 @@
       </c>
       <c r="I9" s="6">
         <f t="shared" ref="I9" si="36">G9</f>
-        <v>-66.263030303030334</v>
+        <v>-66.256888888888838</v>
       </c>
       <c r="K9" s="6">
         <f t="shared" si="28"/>
@@ -6496,14 +6500,14 @@
       </c>
       <c r="M9" s="6">
         <f>M8+L5</f>
-        <v>6610.02</v>
+        <v>6609.2999999999993</v>
       </c>
       <c r="N9" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O9" s="6">
         <f t="shared" si="12"/>
-        <v>6610.02</v>
+        <v>6609.2999999999993</v>
       </c>
       <c r="P9" s="6">
         <f t="shared" si="13"/>
@@ -6511,7 +6515,7 @@
       </c>
       <c r="Q9" s="6">
         <f t="shared" si="14"/>
-        <v>-66.167000000000002</v>
+        <v>-66.155000000000001</v>
       </c>
       <c r="R9" s="6">
         <f t="shared" si="29"/>
@@ -6519,7 +6523,7 @@
       </c>
       <c r="S9" s="6">
         <f t="shared" ref="S9" si="37">Q9</f>
-        <v>-66.167000000000002</v>
+        <v>-66.155000000000001</v>
       </c>
       <c r="U9" s="6">
         <f t="shared" si="31"/>
@@ -6527,22 +6531,22 @@
       </c>
       <c r="V9" s="6">
         <f>V8+$V5</f>
-        <v>4503.603454545454</v>
+        <v>4503.2244000000001</v>
       </c>
       <c r="W9" s="6">
         <v>6514</v>
       </c>
       <c r="X9" s="6">
         <f t="shared" ref="X9:Y9" si="38">X8+X5</f>
-        <v>4514.0142727272723</v>
+        <v>4513.7366000000002</v>
       </c>
       <c r="Y9" s="6">
         <f t="shared" si="38"/>
-        <v>6442.434181818182</v>
+        <v>6442.0154666666658</v>
       </c>
       <c r="Z9" s="6">
         <f t="shared" si="16"/>
-        <v>45.060057575757497</v>
+        <v>45.053739999999998</v>
       </c>
       <c r="AA9" s="6">
         <f t="shared" si="17"/>
@@ -6550,11 +6554,11 @@
       </c>
       <c r="AB9" s="6">
         <f t="shared" si="18"/>
-        <v>45.23357121212117</v>
+        <v>45.228943333333333</v>
       </c>
       <c r="AC9" s="6">
         <f t="shared" si="19"/>
-        <v>-64.707236363636326</v>
+        <v>-64.700257777777836</v>
       </c>
       <c r="AE9" s="6">
         <v>3</v>
@@ -6601,14 +6605,14 @@
       </c>
       <c r="C10" s="6">
         <f>C9+B6</f>
-        <v>6617.1636363636353</v>
+        <v>6616.4266666666663</v>
       </c>
       <c r="D10" s="6">
         <v>4314</v>
       </c>
       <c r="E10" s="6">
         <f t="shared" si="24"/>
-        <v>6617.1636363636353</v>
+        <v>6616.4266666666663</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="25"/>
@@ -6616,7 +6620,7 @@
       </c>
       <c r="G10" s="6">
         <f t="shared" si="26"/>
-        <v>-66.286060606060673</v>
+        <v>-66.273777777777838</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="35"/>
@@ -6624,7 +6628,7 @@
       </c>
       <c r="I10" s="6">
         <f t="shared" ref="I10" si="40">G10</f>
-        <v>-66.286060606060673</v>
+        <v>-66.273777777777838</v>
       </c>
       <c r="K10" s="6">
         <f t="shared" si="28"/>
@@ -6635,14 +6639,14 @@
       </c>
       <c r="M10" s="6">
         <f>M9+L5</f>
-        <v>6611.2800000000007</v>
+        <v>6610.1999999999989</v>
       </c>
       <c r="N10" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O10" s="6">
         <f t="shared" si="12"/>
-        <v>6611.2800000000007</v>
+        <v>6610.1999999999989</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="13"/>
@@ -6650,7 +6654,7 @@
       </c>
       <c r="Q10" s="6">
         <f t="shared" si="14"/>
-        <v>-66.188000000000002</v>
+        <v>-66.17</v>
       </c>
       <c r="R10" s="6">
         <f t="shared" si="29"/>
@@ -6658,7 +6662,7 @@
       </c>
       <c r="S10" s="6">
         <f t="shared" ref="S10" si="41">Q10</f>
-        <v>-66.188000000000002</v>
+        <v>-66.17</v>
       </c>
       <c r="U10" s="6">
         <f t="shared" si="31"/>
@@ -6666,22 +6670,22 @@
       </c>
       <c r="V10" s="6">
         <f>V9+$V5</f>
-        <v>4504.3141818181812</v>
+        <v>4503.7456000000002</v>
       </c>
       <c r="W10" s="6">
         <v>6514</v>
       </c>
       <c r="X10" s="6">
         <f t="shared" ref="X10:Y10" si="42">X9+X5</f>
-        <v>4514.5349090909085</v>
+        <v>4514.1184000000003</v>
       </c>
       <c r="Y10" s="6">
         <f t="shared" si="42"/>
-        <v>6443.2192727272732</v>
+        <v>6442.5911999999989</v>
       </c>
       <c r="Z10" s="6">
         <f t="shared" si="16"/>
-        <v>45.071903030302998</v>
+        <v>45.062426666666667</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="17"/>
@@ -6689,11 +6693,11 @@
       </c>
       <c r="AB10" s="6">
         <f t="shared" si="18"/>
-        <v>45.242248484848503</v>
+        <v>45.235306666666666</v>
       </c>
       <c r="AC10" s="6">
         <f t="shared" si="19"/>
-        <v>-64.720321212121164</v>
+        <v>-64.709853333333328</v>
       </c>
       <c r="AE10" s="6">
         <v>4</v>
@@ -6740,14 +6744,14 @@
       </c>
       <c r="C11" s="6">
         <f>C10+B6</f>
-        <v>6618.5454545454531</v>
+        <v>6617.44</v>
       </c>
       <c r="D11" s="6">
         <v>4314</v>
       </c>
       <c r="E11" s="6">
         <f t="shared" si="24"/>
-        <v>6618.5454545454531</v>
+        <v>6617.44</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="25"/>
@@ -6755,7 +6759,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="26"/>
-        <v>-66.309090909090827</v>
+        <v>-66.290666666666667</v>
       </c>
       <c r="H11" s="6">
         <f t="shared" si="35"/>
@@ -6763,7 +6767,7 @@
       </c>
       <c r="I11" s="6">
         <f t="shared" ref="I11" si="44">G11</f>
-        <v>-66.309090909090827</v>
+        <v>-66.290666666666667</v>
       </c>
       <c r="K11" s="6">
         <f t="shared" si="28"/>
@@ -6774,14 +6778,14 @@
       </c>
       <c r="M11" s="6">
         <f>M10+L5</f>
-        <v>6612.5400000000009</v>
+        <v>6611.0999999999985</v>
       </c>
       <c r="N11" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O11" s="6">
         <f t="shared" si="12"/>
-        <v>6612.5400000000009</v>
+        <v>6611.0999999999985</v>
       </c>
       <c r="P11" s="6">
         <f t="shared" si="13"/>
@@ -6789,7 +6793,7 @@
       </c>
       <c r="Q11" s="6">
         <f t="shared" si="14"/>
-        <v>-66.209000000000003</v>
+        <v>-66.185000000000002</v>
       </c>
       <c r="R11" s="6">
         <f t="shared" si="29"/>
@@ -6797,7 +6801,7 @@
       </c>
       <c r="S11" s="6">
         <f t="shared" ref="S11" si="45">Q11</f>
-        <v>-66.209000000000003</v>
+        <v>-66.185000000000002</v>
       </c>
       <c r="U11" s="6">
         <f t="shared" si="31"/>
@@ -6805,22 +6809,22 @@
       </c>
       <c r="V11" s="6">
         <f>V10+$V5</f>
-        <v>4505.0249090909083</v>
+        <v>4504.2668000000003</v>
       </c>
       <c r="W11" s="6">
         <v>6514</v>
       </c>
       <c r="X11" s="6">
         <f t="shared" ref="X11:Y11" si="46">X10+X5</f>
-        <v>4515.0555454545447</v>
+        <v>4514.5002000000004</v>
       </c>
       <c r="Y11" s="6">
         <f t="shared" si="46"/>
-        <v>6444.0043636363644</v>
+        <v>6443.1669333333321</v>
       </c>
       <c r="Z11" s="6">
         <f t="shared" si="16"/>
-        <v>45.083748484848499</v>
+        <v>45.071113333333336</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="17"/>
@@ -6828,11 +6832,11 @@
       </c>
       <c r="AB11" s="6">
         <f t="shared" si="18"/>
-        <v>45.250925757575665</v>
+        <v>45.241669999999999</v>
       </c>
       <c r="AC11" s="6">
         <f t="shared" si="19"/>
-        <v>-64.733406060606001</v>
+        <v>-64.719448888888834</v>
       </c>
       <c r="AE11" s="6" t="s">
         <v>28</v>
@@ -6876,14 +6880,14 @@
       </c>
       <c r="C12" s="6">
         <f>C11+B6</f>
-        <v>6619.927272727271</v>
+        <v>6618.4533333333329</v>
       </c>
       <c r="D12" s="6">
         <v>4314</v>
       </c>
       <c r="E12" s="6">
         <f t="shared" si="24"/>
-        <v>6619.927272727271</v>
+        <v>6618.4533333333329</v>
       </c>
       <c r="F12" s="6">
         <f t="shared" si="25"/>
@@ -6891,7 +6895,7 @@
       </c>
       <c r="G12" s="6">
         <f t="shared" si="26"/>
-        <v>-66.332121212121166</v>
+        <v>-66.307555555555496</v>
       </c>
       <c r="H12" s="6">
         <f t="shared" si="35"/>
@@ -6899,7 +6903,7 @@
       </c>
       <c r="I12" s="6">
         <f t="shared" ref="I12" si="51">G12</f>
-        <v>-66.332121212121166</v>
+        <v>-66.307555555555496</v>
       </c>
       <c r="K12" s="6">
         <f t="shared" si="28"/>
@@ -6910,14 +6914,14 @@
       </c>
       <c r="M12" s="6">
         <f>M11+L5</f>
-        <v>6613.8000000000011</v>
+        <v>6611.9999999999982</v>
       </c>
       <c r="N12" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O12" s="6">
         <f t="shared" si="12"/>
-        <v>6613.8000000000011</v>
+        <v>6611.9999999999982</v>
       </c>
       <c r="P12" s="6">
         <f t="shared" si="13"/>
@@ -6925,7 +6929,7 @@
       </c>
       <c r="Q12" s="6">
         <f t="shared" si="14"/>
-        <v>-66.23</v>
+        <v>-66.2</v>
       </c>
       <c r="R12" s="6">
         <f t="shared" si="29"/>
@@ -6933,7 +6937,7 @@
       </c>
       <c r="S12" s="6">
         <f t="shared" ref="S12" si="52">Q12</f>
-        <v>-66.23</v>
+        <v>-66.2</v>
       </c>
       <c r="U12" s="6">
         <f t="shared" si="31"/>
@@ -6941,22 +6945,22 @@
       </c>
       <c r="V12" s="6">
         <f>V11+$V5</f>
-        <v>4505.7356363636354</v>
+        <v>4504.7880000000005</v>
       </c>
       <c r="W12" s="6">
         <v>6514</v>
       </c>
       <c r="X12" s="6">
         <f t="shared" ref="X12:Y12" si="53">X11+X5</f>
-        <v>4515.5761818181809</v>
+        <v>4514.8820000000005</v>
       </c>
       <c r="Y12" s="6">
         <f t="shared" si="53"/>
-        <v>6444.7894545454556</v>
+        <v>6443.7426666666652</v>
       </c>
       <c r="Z12" s="6">
         <f t="shared" si="16"/>
-        <v>45.095593939394</v>
+        <v>45.079799999999999</v>
       </c>
       <c r="AA12" s="6">
         <f t="shared" si="17"/>
@@ -6964,11 +6968,11 @@
       </c>
       <c r="AB12" s="6">
         <f t="shared" si="18"/>
-        <v>45.259603030302998</v>
+        <v>45.248033333333332</v>
       </c>
       <c r="AC12" s="6">
         <f t="shared" si="19"/>
-        <v>-64.746490909090994</v>
+        <v>-64.729044444444497</v>
       </c>
     </row>
     <row r="13" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
@@ -6981,14 +6985,14 @@
       </c>
       <c r="C13" s="6">
         <f>C12+B6</f>
-        <v>6621.3090909090888</v>
+        <v>6619.4666666666662</v>
       </c>
       <c r="D13" s="6">
         <v>4314</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" si="24"/>
-        <v>6621.3090909090888</v>
+        <v>6619.4666666666662</v>
       </c>
       <c r="F13" s="6">
         <f t="shared" si="25"/>
@@ -6996,7 +7000,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="26"/>
-        <v>-66.355151515151505</v>
+        <v>-66.324444444444495</v>
       </c>
       <c r="H13" s="6">
         <f t="shared" si="35"/>
@@ -7004,7 +7008,7 @@
       </c>
       <c r="I13" s="6">
         <f t="shared" ref="I13" si="54">G13</f>
-        <v>-66.355151515151505</v>
+        <v>-66.324444444444495</v>
       </c>
       <c r="K13" s="6">
         <f t="shared" si="28"/>
@@ -7015,14 +7019,14 @@
       </c>
       <c r="M13" s="6">
         <f>M12+L5</f>
-        <v>6615.0600000000013</v>
+        <v>6612.8999999999978</v>
       </c>
       <c r="N13" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O13" s="6">
         <f t="shared" si="12"/>
-        <v>6615.0600000000013</v>
+        <v>6612.8999999999978</v>
       </c>
       <c r="P13" s="6">
         <f t="shared" si="13"/>
@@ -7030,7 +7034,7 @@
       </c>
       <c r="Q13" s="6">
         <f t="shared" si="14"/>
-        <v>-66.251000000000005</v>
+        <v>-66.215000000000003</v>
       </c>
       <c r="R13" s="6">
         <f t="shared" si="29"/>
@@ -7038,7 +7042,7 @@
       </c>
       <c r="S13" s="6">
         <f t="shared" ref="S13" si="55">Q13</f>
-        <v>-66.251000000000005</v>
+        <v>-66.215000000000003</v>
       </c>
       <c r="U13" s="6">
         <f t="shared" si="31"/>
@@ -7046,22 +7050,22 @@
       </c>
       <c r="V13" s="6">
         <f>V12+$V5</f>
-        <v>4506.4463636363625</v>
+        <v>4505.3092000000006</v>
       </c>
       <c r="W13" s="6">
         <v>6514</v>
       </c>
       <c r="X13" s="6">
         <f t="shared" ref="X13:Y13" si="56">X12+X5</f>
-        <v>4516.0968181818171</v>
+        <v>4515.2638000000006</v>
       </c>
       <c r="Y13" s="6">
         <f t="shared" si="56"/>
-        <v>6445.5745454545468</v>
+        <v>6444.3183999999983</v>
       </c>
       <c r="Z13" s="6">
         <f t="shared" si="16"/>
-        <v>45.10743939393933</v>
+        <v>45.088486666666668</v>
       </c>
       <c r="AA13" s="6">
         <f t="shared" si="17"/>
@@ -7069,11 +7073,11 @@
       </c>
       <c r="AB13" s="6">
         <f t="shared" si="18"/>
-        <v>45.26828030303033</v>
+        <v>45.254396666666665</v>
       </c>
       <c r="AC13" s="6">
         <f t="shared" si="19"/>
-        <v>-64.759575757575831</v>
+        <v>-64.738640000000004</v>
       </c>
       <c r="AE13" s="8" t="s">
         <v>29</v>
@@ -7089,14 +7093,14 @@
       </c>
       <c r="C14" s="6">
         <f>C13+B6</f>
-        <v>6622.6909090909066</v>
+        <v>6620.48</v>
       </c>
       <c r="D14" s="6">
         <v>4314</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" si="24"/>
-        <v>6622.6909090909066</v>
+        <v>6620.48</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="25"/>
@@ -7104,7 +7108,7 @@
       </c>
       <c r="G14" s="6">
         <f t="shared" si="26"/>
-        <v>-66.378181818181829</v>
+        <v>-66.341333333333338</v>
       </c>
       <c r="H14" s="6">
         <f t="shared" si="35"/>
@@ -7112,7 +7116,7 @@
       </c>
       <c r="I14" s="6">
         <f t="shared" ref="I14" si="57">G14</f>
-        <v>-66.378181818181829</v>
+        <v>-66.341333333333338</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="28"/>
@@ -7123,14 +7127,14 @@
       </c>
       <c r="M14" s="6">
         <f>M13+L5</f>
-        <v>6616.3200000000015</v>
+        <v>6613.7999999999975</v>
       </c>
       <c r="N14" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O14" s="6">
         <f t="shared" si="12"/>
-        <v>6616.3200000000015</v>
+        <v>6613.7999999999975</v>
       </c>
       <c r="P14" s="6">
         <f t="shared" si="13"/>
@@ -7138,7 +7142,7 @@
       </c>
       <c r="Q14" s="6">
         <f t="shared" si="14"/>
-        <v>-66.272000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="R14" s="6">
         <f t="shared" si="29"/>
@@ -7146,7 +7150,7 @@
       </c>
       <c r="S14" s="6">
         <f t="shared" ref="S14" si="58">Q14</f>
-        <v>-66.272000000000006</v>
+        <v>-66.23</v>
       </c>
       <c r="U14" s="6">
         <f t="shared" si="31"/>
@@ -7154,22 +7158,22 @@
       </c>
       <c r="V14" s="6">
         <f>V13+$V5</f>
-        <v>4507.1570909090897</v>
+        <v>4505.8304000000007</v>
       </c>
       <c r="W14" s="6">
         <v>6514</v>
       </c>
       <c r="X14" s="6">
         <f t="shared" ref="X14:Y14" si="59">X13+X5</f>
-        <v>4516.6174545454533</v>
+        <v>4515.6456000000007</v>
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="59"/>
-        <v>6446.3596363636379</v>
+        <v>6444.8941333333314</v>
       </c>
       <c r="Z14" s="6">
         <f t="shared" si="16"/>
-        <v>45.119284848484831</v>
+        <v>45.09717333333333</v>
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="17"/>
@@ -7177,11 +7181,11 @@
       </c>
       <c r="AB14" s="6">
         <f t="shared" si="18"/>
-        <v>45.2769575757575</v>
+        <v>45.260759999999998</v>
       </c>
       <c r="AC14" s="6">
         <f t="shared" si="19"/>
-        <v>-64.772660606060668</v>
+        <v>-64.748235555555496</v>
       </c>
       <c r="AE14" s="6" t="s">
         <v>21</v>
@@ -7221,14 +7225,14 @@
       </c>
       <c r="C15" s="6">
         <f>C14+B6</f>
-        <v>6624.0727272727245</v>
+        <v>6621.4933333333329</v>
       </c>
       <c r="D15" s="6">
         <v>4314</v>
       </c>
       <c r="E15" s="6">
         <f t="shared" si="24"/>
-        <v>6624.0727272727245</v>
+        <v>6621.4933333333329</v>
       </c>
       <c r="F15" s="6">
         <f t="shared" si="25"/>
@@ -7236,7 +7240,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="26"/>
-        <v>-66.401212121211998</v>
+        <v>-66.358222222222167</v>
       </c>
       <c r="H15" s="6">
         <f t="shared" si="35"/>
@@ -7244,7 +7248,7 @@
       </c>
       <c r="I15" s="6">
         <f t="shared" ref="I15" si="60">G15</f>
-        <v>-66.401212121211998</v>
+        <v>-66.358222222222167</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="28"/>
@@ -7255,14 +7259,14 @@
       </c>
       <c r="M15" s="6">
         <f>M14+L5</f>
-        <v>6617.5800000000017</v>
+        <v>6614.6999999999971</v>
       </c>
       <c r="N15" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O15" s="6">
         <f t="shared" si="12"/>
-        <v>6617.5800000000017</v>
+        <v>6614.6999999999971</v>
       </c>
       <c r="P15" s="6">
         <f t="shared" si="13"/>
@@ -7270,7 +7274,7 @@
       </c>
       <c r="Q15" s="6">
         <f t="shared" si="14"/>
-        <v>-66.293000000000006</v>
+        <v>-66.245000000000005</v>
       </c>
       <c r="R15" s="6">
         <f t="shared" si="29"/>
@@ -7278,7 +7282,7 @@
       </c>
       <c r="S15" s="6">
         <f t="shared" ref="S15" si="61">Q15</f>
-        <v>-66.293000000000006</v>
+        <v>-66.245000000000005</v>
       </c>
       <c r="U15" s="6">
         <f t="shared" si="31"/>
@@ -7286,22 +7290,22 @@
       </c>
       <c r="V15" s="6">
         <f>V14+$V5</f>
-        <v>4507.8678181818168</v>
+        <v>4506.3516000000009</v>
       </c>
       <c r="W15" s="6">
         <v>6514</v>
       </c>
       <c r="X15" s="6">
         <f t="shared" ref="X15:Y15" si="62">X14+X5</f>
-        <v>4517.1380909090894</v>
+        <v>4516.0274000000009</v>
       </c>
       <c r="Y15" s="6">
         <f t="shared" si="62"/>
-        <v>6447.1447272727291</v>
+        <v>6445.4698666666645</v>
       </c>
       <c r="Z15" s="6">
         <f t="shared" si="16"/>
-        <v>45.131130303030332</v>
+        <v>45.10586</v>
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="17"/>
@@ -7309,11 +7313,11 @@
       </c>
       <c r="AB15" s="6">
         <f t="shared" si="18"/>
-        <v>45.285634848484833</v>
+        <v>45.26712333333333</v>
       </c>
       <c r="AC15" s="6">
         <f t="shared" si="19"/>
-        <v>-64.785745454545506</v>
+        <v>-64.757831111111003</v>
       </c>
       <c r="AE15" s="6" t="s">
         <v>23</v>
@@ -7343,14 +7347,14 @@
       </c>
       <c r="C16" s="6">
         <f>C15+B6</f>
-        <v>6625.4545454545423</v>
+        <v>6622.5066666666662</v>
       </c>
       <c r="D16" s="6">
         <v>4314</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" si="24"/>
-        <v>6625.4545454545423</v>
+        <v>6622.5066666666662</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="25"/>
@@ -7358,7 +7362,7 @@
       </c>
       <c r="G16" s="6">
         <f t="shared" si="26"/>
-        <v>-66.424242424242337</v>
+        <v>-66.375111111111167</v>
       </c>
       <c r="H16" s="6">
         <f t="shared" si="35"/>
@@ -7366,7 +7370,7 @@
       </c>
       <c r="I16" s="6">
         <f t="shared" ref="I16" si="63">G16</f>
-        <v>-66.424242424242337</v>
+        <v>-66.375111111111167</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="28"/>
@@ -7377,14 +7381,14 @@
       </c>
       <c r="M16" s="6">
         <f>M15+L5</f>
-        <v>6618.840000000002</v>
+        <v>6615.5999999999967</v>
       </c>
       <c r="N16" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O16" s="6">
         <f t="shared" si="12"/>
-        <v>6618.840000000002</v>
+        <v>6615.5999999999967</v>
       </c>
       <c r="P16" s="6">
         <f t="shared" si="13"/>
@@ -7392,7 +7396,7 @@
       </c>
       <c r="Q16" s="6">
         <f t="shared" si="14"/>
-        <v>-66.313999999999993</v>
+        <v>-66.260000000000005</v>
       </c>
       <c r="R16" s="6">
         <f t="shared" si="29"/>
@@ -7400,7 +7404,7 @@
       </c>
       <c r="S16" s="6">
         <f t="shared" ref="S16" si="64">Q16</f>
-        <v>-66.313999999999993</v>
+        <v>-66.260000000000005</v>
       </c>
       <c r="U16" s="6">
         <f t="shared" si="31"/>
@@ -7408,22 +7412,22 @@
       </c>
       <c r="V16" s="6">
         <f>V15+$V5</f>
-        <v>4508.5785454545439</v>
+        <v>4506.872800000001</v>
       </c>
       <c r="W16" s="6">
         <v>6514</v>
       </c>
       <c r="X16" s="6">
         <f t="shared" ref="X16:Y16" si="65">X15+X5</f>
-        <v>4517.6587272727256</v>
+        <v>4516.409200000001</v>
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="65"/>
-        <v>6447.9298181818203</v>
+        <v>6446.0455999999976</v>
       </c>
       <c r="Z16" s="6">
         <f t="shared" si="16"/>
-        <v>45.14297575757567</v>
+        <v>45.114546666666669</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="17"/>
@@ -7431,11 +7435,11 @@
       </c>
       <c r="AB16" s="6">
         <f t="shared" si="18"/>
-        <v>45.294312121212165</v>
+        <v>45.273486666666663</v>
       </c>
       <c r="AC16" s="6">
         <f t="shared" si="19"/>
-        <v>-64.798830303030329</v>
+        <v>-64.767426666666665</v>
       </c>
       <c r="AE16" s="6" t="s">
         <v>24</v>
@@ -7472,14 +7476,14 @@
       </c>
       <c r="C17" s="6">
         <f>C16+B6</f>
-        <v>6626.8363636363601</v>
+        <v>6623.5199999999995</v>
       </c>
       <c r="D17" s="6">
         <v>4314</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" si="24"/>
-        <v>6626.8363636363601</v>
+        <v>6623.5199999999995</v>
       </c>
       <c r="F17" s="6">
         <f t="shared" si="25"/>
@@ -7487,7 +7491,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="26"/>
-        <v>-66.447272727272662</v>
+        <v>-66.391999999999996</v>
       </c>
       <c r="H17" s="6">
         <f t="shared" si="35"/>
@@ -7495,7 +7499,7 @@
       </c>
       <c r="I17" s="6">
         <f t="shared" ref="I17" si="67">G17</f>
-        <v>-66.447272727272662</v>
+        <v>-66.391999999999996</v>
       </c>
       <c r="K17" s="6">
         <f t="shared" si="28"/>
@@ -7506,14 +7510,14 @@
       </c>
       <c r="M17" s="6">
         <f>M16+L5</f>
-        <v>6620.1000000000022</v>
+        <v>6616.4999999999964</v>
       </c>
       <c r="N17" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O17" s="6">
         <f t="shared" si="12"/>
-        <v>6620.1000000000022</v>
+        <v>6616.4999999999964</v>
       </c>
       <c r="P17" s="6">
         <f t="shared" si="13"/>
@@ -7521,7 +7525,7 @@
       </c>
       <c r="Q17" s="6">
         <f t="shared" si="14"/>
-        <v>-66.334999999999994</v>
+        <v>-66.275000000000006</v>
       </c>
       <c r="R17" s="6">
         <f t="shared" si="29"/>
@@ -7529,7 +7533,7 @@
       </c>
       <c r="S17" s="6">
         <f t="shared" ref="S17" si="68">Q17</f>
-        <v>-66.334999999999994</v>
+        <v>-66.275000000000006</v>
       </c>
       <c r="U17" s="6">
         <f t="shared" si="31"/>
@@ -7537,22 +7541,22 @@
       </c>
       <c r="V17" s="6">
         <f>V16+$V5</f>
-        <v>4509.2892727272711</v>
+        <v>4507.3940000000011</v>
       </c>
       <c r="W17" s="6">
         <v>6514</v>
       </c>
       <c r="X17" s="6">
         <f t="shared" ref="X17:Y17" si="69">X16+X5</f>
-        <v>4518.1793636363618</v>
+        <v>4516.7910000000011</v>
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="69"/>
-        <v>6448.7149090909115</v>
+        <v>6446.6213333333308</v>
       </c>
       <c r="Z17" s="6">
         <f t="shared" si="16"/>
-        <v>45.154821212121163</v>
+        <v>45.123233333333332</v>
       </c>
       <c r="AA17" s="6">
         <f t="shared" si="17"/>
@@ -7560,11 +7564,11 @@
       </c>
       <c r="AB17" s="6">
         <f t="shared" si="18"/>
-        <v>45.302989393939335</v>
+        <v>45.279850000000003</v>
       </c>
       <c r="AC17" s="6">
         <f t="shared" si="19"/>
-        <v>-64.811915151515166</v>
+        <v>-64.777022222222172</v>
       </c>
       <c r="AE17" s="6" t="s">
         <v>25</v>
@@ -7604,14 +7608,14 @@
       </c>
       <c r="C18" s="6">
         <f>C17+B6</f>
-        <v>6628.218181818178</v>
+        <v>6624.5333333333328</v>
       </c>
       <c r="D18" s="6">
         <v>4314</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="24"/>
-        <v>6628.218181818178</v>
+        <v>6624.5333333333328</v>
       </c>
       <c r="F18" s="6">
         <f t="shared" si="25"/>
@@ -7619,7 +7623,7 @@
       </c>
       <c r="G18" s="6">
         <f t="shared" si="26"/>
-        <v>-66.470303030303</v>
+        <v>-66.408888888888839</v>
       </c>
       <c r="H18" s="6">
         <f t="shared" si="35"/>
@@ -7627,7 +7631,7 @@
       </c>
       <c r="I18" s="6">
         <f t="shared" ref="I18" si="70">G18</f>
-        <v>-66.470303030303</v>
+        <v>-66.408888888888839</v>
       </c>
       <c r="K18" s="6">
         <f t="shared" si="28"/>
@@ -7638,14 +7642,14 @@
       </c>
       <c r="M18" s="6">
         <f>M17+L5</f>
-        <v>6621.3600000000024</v>
+        <v>6617.399999999996</v>
       </c>
       <c r="N18" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O18" s="6">
         <f t="shared" si="12"/>
-        <v>6621.3600000000024</v>
+        <v>6617.399999999996</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="13"/>
@@ -7653,7 +7657,7 @@
       </c>
       <c r="Q18" s="6">
         <f t="shared" si="14"/>
-        <v>-66.355999999999995</v>
+        <v>-66.290000000000006</v>
       </c>
       <c r="R18" s="6">
         <f t="shared" si="29"/>
@@ -7661,7 +7665,7 @@
       </c>
       <c r="S18" s="6">
         <f t="shared" ref="S18" si="71">Q18</f>
-        <v>-66.355999999999995</v>
+        <v>-66.290000000000006</v>
       </c>
       <c r="U18" s="6">
         <f t="shared" si="31"/>
@@ -7669,22 +7673,22 @@
       </c>
       <c r="V18" s="6">
         <f>V17+$V5</f>
-        <v>4509.9999999999982</v>
+        <v>4507.9152000000013</v>
       </c>
       <c r="W18" s="6">
         <v>6514</v>
       </c>
       <c r="X18" s="9">
         <f t="shared" ref="X18:Y18" si="72">X17+X5</f>
-        <v>4518.699999999998</v>
+        <v>4517.1728000000012</v>
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="72"/>
-        <v>6449.5000000000027</v>
+        <v>6447.1970666666639</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="16"/>
-        <v>45.166666666666664</v>
+        <v>45.131920000000001</v>
       </c>
       <c r="AA18" s="6">
         <f t="shared" si="17"/>
@@ -7692,11 +7696,11 @@
       </c>
       <c r="AB18" s="6">
         <f t="shared" si="18"/>
-        <v>45.311666666666667</v>
+        <v>45.286213333333336</v>
       </c>
       <c r="AC18" s="6">
         <f t="shared" si="19"/>
-        <v>-64.825000000000003</v>
+        <v>-64.786617777777664</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>27</v>
@@ -7724,14 +7728,14 @@
       </c>
       <c r="C19" s="6">
         <f>C18+B6</f>
-        <v>6629.5999999999958</v>
+        <v>6625.5466666666662</v>
       </c>
       <c r="D19" s="6">
         <v>4314</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="24"/>
-        <v>6629.5999999999958</v>
+        <v>6625.5466666666662</v>
       </c>
       <c r="F19" s="6">
         <f t="shared" si="25"/>
@@ -7739,7 +7743,7 @@
       </c>
       <c r="G19" s="6">
         <f t="shared" si="26"/>
-        <v>-66.493333333333339</v>
+        <v>-66.425777777777839</v>
       </c>
       <c r="H19" s="6">
         <f t="shared" si="35"/>
@@ -7747,7 +7751,7 @@
       </c>
       <c r="I19" s="6">
         <f t="shared" ref="I19" si="73">G19</f>
-        <v>-66.493333333333339</v>
+        <v>-66.425777777777839</v>
       </c>
       <c r="K19" s="6">
         <f t="shared" si="28"/>
@@ -7758,14 +7762,14 @@
       </c>
       <c r="M19" s="6">
         <f>M18+L5</f>
-        <v>6622.6200000000026</v>
+        <v>6618.2999999999956</v>
       </c>
       <c r="N19" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O19" s="6">
         <f t="shared" si="12"/>
-        <v>6622.6200000000026</v>
+        <v>6618.2999999999956</v>
       </c>
       <c r="P19" s="6">
         <f t="shared" si="13"/>
@@ -7773,7 +7777,7 @@
       </c>
       <c r="Q19" s="6">
         <f t="shared" si="14"/>
-        <v>-66.376999999999995</v>
+        <v>-66.305000000000007</v>
       </c>
       <c r="R19" s="6">
         <f t="shared" si="29"/>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="S19" s="6">
         <f t="shared" ref="S19" si="74">Q19</f>
-        <v>-66.376999999999995</v>
+        <v>-66.305000000000007</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="31"/>
@@ -7789,22 +7793,22 @@
       </c>
       <c r="V19" s="6">
         <f>V18+$V5</f>
-        <v>4510.7107272727253</v>
+        <v>4508.4364000000014</v>
       </c>
       <c r="W19" s="6">
         <v>6514</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" ref="X19:Y19" si="75">X18+X5</f>
-        <v>4519.2206363636342</v>
+        <v>4517.5546000000013</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="75"/>
-        <v>6450.2850909090939</v>
+        <v>6447.772799999997</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="16"/>
-        <v>45.178512121212165</v>
+        <v>45.140606666666663</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="17"/>
@@ -7812,11 +7816,11 @@
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="18"/>
-        <v>45.320343939393837</v>
+        <v>45.292576666666669</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="19"/>
-        <v>-64.83808484848484</v>
+        <v>-64.796213333333327</v>
       </c>
       <c r="AE19" s="6">
         <v>1</v>
@@ -7860,14 +7864,14 @@
       </c>
       <c r="C20" s="6">
         <f>C19+B6</f>
-        <v>6630.9818181818137</v>
+        <v>6626.5599999999995</v>
       </c>
       <c r="D20" s="6">
         <v>4314</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="24"/>
-        <v>6630.9818181818137</v>
+        <v>6626.5599999999995</v>
       </c>
       <c r="F20" s="6">
         <f t="shared" si="25"/>
@@ -7875,7 +7879,7 @@
       </c>
       <c r="G20" s="6">
         <f t="shared" si="26"/>
-        <v>-66.516363636363494</v>
+        <v>-66.442666666666668</v>
       </c>
       <c r="H20" s="6">
         <f t="shared" si="35"/>
@@ -7883,7 +7887,7 @@
       </c>
       <c r="I20" s="6">
         <f t="shared" ref="I20" si="77">G20</f>
-        <v>-66.516363636363494</v>
+        <v>-66.442666666666668</v>
       </c>
       <c r="K20" s="6">
         <f t="shared" si="28"/>
@@ -7894,14 +7898,14 @@
       </c>
       <c r="M20" s="6">
         <f>M19+L5</f>
-        <v>6623.8800000000028</v>
+        <v>6619.1999999999953</v>
       </c>
       <c r="N20" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O20" s="6">
         <f t="shared" si="12"/>
-        <v>6623.8800000000028</v>
+        <v>6619.1999999999953</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="13"/>
@@ -7909,7 +7913,7 @@
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="14"/>
-        <v>-66.397999999999996</v>
+        <v>-66.319999999999993</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="29"/>
@@ -7917,7 +7921,7 @@
       </c>
       <c r="S20" s="6">
         <f t="shared" ref="S20" si="78">Q20</f>
-        <v>-66.397999999999996</v>
+        <v>-66.319999999999993</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="31"/>
@@ -7925,22 +7929,22 @@
       </c>
       <c r="V20" s="6">
         <f>V19+$V5</f>
-        <v>4511.4214545454524</v>
+        <v>4508.9576000000015</v>
       </c>
       <c r="W20" s="6">
         <v>6514</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" ref="X20:Y20" si="79">X19+X5</f>
-        <v>4519.7412727272704</v>
+        <v>4517.9364000000014</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="79"/>
-        <v>6451.0701818181851</v>
+        <v>6448.3485333333301</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="16"/>
-        <v>45.190357575757503</v>
+        <v>45.149293333333333</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="17"/>
@@ -7948,11 +7952,11 @@
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="18"/>
-        <v>45.32902121212117</v>
+        <v>45.298940000000002</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="19"/>
-        <v>-64.851169696969833</v>
+        <v>-64.805808888888834</v>
       </c>
       <c r="AE20" s="6">
         <v>2</v>
@@ -7996,14 +8000,14 @@
       </c>
       <c r="C21" s="6">
         <f>C20+B6</f>
-        <v>6632.3636363636315</v>
+        <v>6627.5733333333328</v>
       </c>
       <c r="D21" s="6">
         <v>4314</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" si="24"/>
-        <v>6632.3636363636315</v>
+        <v>6627.5733333333328</v>
       </c>
       <c r="F21" s="6">
         <f t="shared" si="25"/>
@@ -8011,7 +8015,7 @@
       </c>
       <c r="G21" s="6">
         <f t="shared" si="26"/>
-        <v>-66.539393939393833</v>
+        <v>-66.459555555555497</v>
       </c>
       <c r="H21" s="6">
         <f t="shared" si="35"/>
@@ -8019,7 +8023,7 @@
       </c>
       <c r="I21" s="6">
         <f t="shared" ref="I21" si="83">G21</f>
-        <v>-66.539393939393833</v>
+        <v>-66.459555555555497</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="28"/>
@@ -8030,14 +8034,14 @@
       </c>
       <c r="M21" s="6">
         <f>M20+L5</f>
-        <v>6625.1400000000031</v>
+        <v>6620.0999999999949</v>
       </c>
       <c r="N21" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O21" s="6">
         <f t="shared" si="12"/>
-        <v>6625.1400000000031</v>
+        <v>6620.0999999999949</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="13"/>
@@ -8045,7 +8049,7 @@
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="14"/>
-        <v>-66.418999999999997</v>
+        <v>-66.334999999999837</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="29"/>
@@ -8053,7 +8057,7 @@
       </c>
       <c r="S21" s="6">
         <f t="shared" ref="S21" si="84">Q21</f>
-        <v>-66.418999999999997</v>
+        <v>-66.334999999999837</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="31"/>
@@ -8061,22 +8065,22 @@
       </c>
       <c r="V21" s="6">
         <f>V20+$V5</f>
-        <v>4512.1321818181796</v>
+        <v>4509.4788000000017</v>
       </c>
       <c r="W21" s="6">
         <v>6514</v>
       </c>
       <c r="X21" s="6">
         <f t="shared" ref="X21:Y21" si="85">X20+X5</f>
-        <v>4520.2619090909066</v>
+        <v>4518.3182000000015</v>
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="85"/>
-        <v>6451.8552727272763</v>
+        <v>6448.9242666666632</v>
       </c>
       <c r="Z21" s="6">
         <f t="shared" si="16"/>
-        <v>45.202203030302996</v>
+        <v>45.157980000000002</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="17"/>
@@ -8084,11 +8088,11 @@
       </c>
       <c r="AB21" s="6">
         <f t="shared" si="18"/>
-        <v>45.337698484848502</v>
+        <v>45.305303333333335</v>
       </c>
       <c r="AC21" s="6">
         <f t="shared" si="19"/>
-        <v>-64.864254545454671</v>
+        <v>-64.81540444444434</v>
       </c>
       <c r="AE21" s="6">
         <v>3</v>
@@ -8132,14 +8136,14 @@
       </c>
       <c r="C22" s="6">
         <f>C21+B6</f>
-        <v>6633.7454545454493</v>
+        <v>6628.5866666666661</v>
       </c>
       <c r="D22" s="6">
         <v>4314</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="24"/>
-        <v>6633.7454545454493</v>
+        <v>6628.5866666666661</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="25"/>
@@ -8147,7 +8151,7 @@
       </c>
       <c r="G22" s="6">
         <f t="shared" si="26"/>
-        <v>-66.562424242424171</v>
+        <v>-66.476444444444496</v>
       </c>
       <c r="H22" s="6">
         <f t="shared" si="35"/>
@@ -8155,7 +8159,7 @@
       </c>
       <c r="I22" s="6">
         <f t="shared" ref="I22" si="86">G22</f>
-        <v>-66.562424242424171</v>
+        <v>-66.476444444444496</v>
       </c>
       <c r="K22" s="6">
         <f t="shared" si="28"/>
@@ -8166,14 +8170,14 @@
       </c>
       <c r="M22" s="6">
         <f>M21+L5</f>
-        <v>6626.4000000000033</v>
+        <v>6620.9999999999945</v>
       </c>
       <c r="N22" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O22" s="6">
         <f t="shared" si="12"/>
-        <v>6626.4000000000033</v>
+        <v>6620.9999999999945</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" si="13"/>
@@ -8181,7 +8185,7 @@
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="14"/>
-        <v>-66.44</v>
+        <v>-66.349999999999838</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="29"/>
@@ -8189,7 +8193,7 @@
       </c>
       <c r="S22" s="6">
         <f t="shared" ref="S22" si="87">Q22</f>
-        <v>-66.44</v>
+        <v>-66.349999999999838</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="31"/>
@@ -8197,22 +8201,22 @@
       </c>
       <c r="V22" s="6">
         <f>V21+$V5</f>
-        <v>4512.8429090909067</v>
+        <v>4510.0000000000018</v>
       </c>
       <c r="W22" s="6">
         <v>6514</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" ref="X22:Y22" si="88">X21+X5</f>
-        <v>4520.7825454545427</v>
+        <v>4518.7000000000016</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="88"/>
-        <v>6452.6403636363675</v>
+        <v>6449.4999999999964</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="16"/>
-        <v>45.214048484848497</v>
+        <v>45.166666666666664</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="17"/>
@@ -8220,11 +8224,11 @@
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="18"/>
-        <v>45.346375757575665</v>
+        <v>45.311666666666667</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="19"/>
-        <v>-64.877339393939494</v>
+        <v>-64.825000000000003</v>
       </c>
       <c r="AE22" s="6">
         <v>4</v>
@@ -8268,14 +8272,14 @@
       </c>
       <c r="C23" s="6">
         <f>C22+B6</f>
-        <v>6635.1272727272672</v>
+        <v>6629.5999999999995</v>
       </c>
       <c r="D23" s="6">
         <v>4314</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="24"/>
-        <v>6635.1272727272672</v>
+        <v>6629.5999999999995</v>
       </c>
       <c r="F23" s="6">
         <f t="shared" si="25"/>
@@ -8283,7 +8287,7 @@
       </c>
       <c r="G23" s="6">
         <f t="shared" si="26"/>
-        <v>-66.585454545454496</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="H23" s="6">
         <f t="shared" si="35"/>
@@ -8291,7 +8295,7 @@
       </c>
       <c r="I23" s="6">
         <f t="shared" ref="I23" si="89">G23</f>
-        <v>-66.585454545454496</v>
+        <v>-66.493333333333339</v>
       </c>
       <c r="K23" s="6">
         <f t="shared" si="28"/>
@@ -8302,14 +8306,14 @@
       </c>
       <c r="M23" s="6">
         <f>M22+L5</f>
-        <v>6627.6600000000035</v>
+        <v>6621.8999999999942</v>
       </c>
       <c r="N23" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O23" s="6">
         <f t="shared" si="12"/>
-        <v>6627.6600000000035</v>
+        <v>6621.8999999999942</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="13"/>
@@ -8317,7 +8321,7 @@
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="14"/>
-        <v>-66.460999999999999</v>
+        <v>-66.364999999999839</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="29"/>
@@ -8325,7 +8329,7 @@
       </c>
       <c r="S23" s="6">
         <f t="shared" ref="S23" si="90">Q23</f>
-        <v>-66.460999999999999</v>
+        <v>-66.364999999999839</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="31"/>
@@ -8333,22 +8337,22 @@
       </c>
       <c r="V23" s="6">
         <f>V22+$V5</f>
-        <v>4513.5536363636338</v>
+        <v>4510.521200000002</v>
       </c>
       <c r="W23" s="6">
         <v>6514</v>
       </c>
       <c r="X23" s="6">
         <f t="shared" ref="X23:Y23" si="91">X22+X5</f>
-        <v>4521.3031818181789</v>
+        <v>4519.0818000000017</v>
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="91"/>
-        <v>6453.4254545454587</v>
+        <v>6450.0757333333295</v>
       </c>
       <c r="Z23" s="6">
         <f t="shared" si="16"/>
-        <v>45.225893939393835</v>
+        <v>45.175353333333334</v>
       </c>
       <c r="AA23" s="6">
         <f t="shared" si="17"/>
@@ -8356,11 +8360,11 @@
       </c>
       <c r="AB23" s="6">
         <f t="shared" si="18"/>
-        <v>45.355053030302997</v>
+        <v>45.31803</v>
       </c>
       <c r="AC23" s="6">
         <f t="shared" si="19"/>
-        <v>-64.890424242424331</v>
+        <v>-64.834595555555495</v>
       </c>
       <c r="AE23" s="6" t="s">
         <v>28</v>
@@ -8400,14 +8404,14 @@
       </c>
       <c r="C24" s="6">
         <f>C23+B6</f>
-        <v>6636.509090909085</v>
+        <v>6630.6133333333328</v>
       </c>
       <c r="D24" s="6">
         <v>4314</v>
       </c>
       <c r="E24" s="6">
         <f t="shared" si="24"/>
-        <v>6636.509090909085</v>
+        <v>6630.6133333333328</v>
       </c>
       <c r="F24" s="6">
         <f t="shared" si="25"/>
@@ -8415,7 +8419,7 @@
       </c>
       <c r="G24" s="6">
         <f t="shared" si="26"/>
-        <v>-66.608484848484665</v>
+        <v>-66.510222222222168</v>
       </c>
       <c r="H24" s="6">
         <f t="shared" si="35"/>
@@ -8423,7 +8427,7 @@
       </c>
       <c r="I24" s="6">
         <f t="shared" ref="I24" si="92">G24</f>
-        <v>-66.608484848484665</v>
+        <v>-66.510222222222168</v>
       </c>
       <c r="K24" s="6">
         <f t="shared" si="28"/>
@@ -8434,14 +8438,14 @@
       </c>
       <c r="M24" s="6">
         <f>M23+L5</f>
-        <v>6628.9200000000037</v>
+        <v>6622.7999999999938</v>
       </c>
       <c r="N24" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O24" s="6">
         <f t="shared" si="12"/>
-        <v>6628.9200000000037</v>
+        <v>6622.7999999999938</v>
       </c>
       <c r="P24" s="6">
         <f t="shared" si="13"/>
@@ -8449,7 +8453,7 @@
       </c>
       <c r="Q24" s="6">
         <f t="shared" si="14"/>
-        <v>-66.481999999999999</v>
+        <v>-66.379999999999839</v>
       </c>
       <c r="R24" s="6">
         <f t="shared" si="29"/>
@@ -8457,7 +8461,7 @@
       </c>
       <c r="S24" s="6">
         <f t="shared" ref="S24" si="93">Q24</f>
-        <v>-66.481999999999999</v>
+        <v>-66.379999999999839</v>
       </c>
       <c r="U24" s="6">
         <f t="shared" si="31"/>
@@ -8465,22 +8469,22 @@
       </c>
       <c r="V24" s="6">
         <f>V23+$V5</f>
-        <v>4514.2643636363609</v>
+        <v>4511.0424000000021</v>
       </c>
       <c r="W24" s="6">
         <v>6514</v>
       </c>
       <c r="X24" s="6">
         <f t="shared" ref="X24:Y24" si="94">X23+X5</f>
-        <v>4521.8238181818151</v>
+        <v>4519.4636000000019</v>
       </c>
       <c r="Y24" s="6">
         <f t="shared" si="94"/>
-        <v>6454.2105454545499</v>
+        <v>6450.6514666666626</v>
       </c>
       <c r="Z24" s="6">
         <f t="shared" si="16"/>
-        <v>45.237739393939336</v>
+        <v>45.184040000000003</v>
       </c>
       <c r="AA24" s="6">
         <f t="shared" si="17"/>
@@ -8488,11 +8492,11 @@
       </c>
       <c r="AB24" s="6">
         <f t="shared" si="18"/>
-        <v>45.36373030303033</v>
+        <v>45.324393333333333</v>
       </c>
       <c r="AC24" s="6">
         <f t="shared" si="19"/>
-        <v>-64.903509090909168</v>
+        <v>-64.844191111111002</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8505,14 +8509,14 @@
       </c>
       <c r="C25" s="6">
         <f>C24+B6</f>
-        <v>6637.8909090909028</v>
+        <v>6631.6266666666661</v>
       </c>
       <c r="D25" s="6">
         <v>4314</v>
       </c>
       <c r="E25" s="6">
         <f t="shared" si="24"/>
-        <v>6637.8909090909028</v>
+        <v>6631.6266666666661</v>
       </c>
       <c r="F25" s="6">
         <f t="shared" si="25"/>
@@ -8520,7 +8524,7 @@
       </c>
       <c r="G25" s="6">
         <f t="shared" si="26"/>
-        <v>-66.631515151515003</v>
+        <v>-66.527111111111168</v>
       </c>
       <c r="H25" s="6">
         <f t="shared" si="35"/>
@@ -8528,7 +8532,7 @@
       </c>
       <c r="I25" s="6">
         <f t="shared" ref="I25" si="95">G25</f>
-        <v>-66.631515151515003</v>
+        <v>-66.527111111111168</v>
       </c>
       <c r="K25" s="6">
         <f t="shared" si="28"/>
@@ -8539,14 +8543,14 @@
       </c>
       <c r="M25" s="6">
         <f>M24+L5</f>
-        <v>6630.1800000000039</v>
+        <v>6623.6999999999935</v>
       </c>
       <c r="N25" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O25" s="6">
         <f t="shared" si="12"/>
-        <v>6630.1800000000039</v>
+        <v>6623.6999999999935</v>
       </c>
       <c r="P25" s="6">
         <f t="shared" si="13"/>
@@ -8554,7 +8558,7 @@
       </c>
       <c r="Q25" s="6">
         <f t="shared" si="14"/>
-        <v>-66.503</v>
+        <v>-66.39499999999984</v>
       </c>
       <c r="R25" s="6">
         <f t="shared" si="29"/>
@@ -8562,7 +8566,7 @@
       </c>
       <c r="S25" s="6">
         <f t="shared" ref="S25" si="96">Q25</f>
-        <v>-66.503</v>
+        <v>-66.39499999999984</v>
       </c>
       <c r="U25" s="6" t="s">
         <v>28</v>
@@ -8606,14 +8610,14 @@
       </c>
       <c r="C26" s="6">
         <f>C25+B6</f>
-        <v>6639.2727272727207</v>
+        <v>6632.6399999999994</v>
       </c>
       <c r="D26" s="6">
         <v>4314</v>
       </c>
       <c r="E26" s="6">
         <f t="shared" si="24"/>
-        <v>6639.2727272727207</v>
+        <v>6632.6399999999994</v>
       </c>
       <c r="F26" s="6">
         <f t="shared" si="25"/>
@@ -8621,7 +8625,7 @@
       </c>
       <c r="G26" s="6">
         <f t="shared" si="26"/>
-        <v>-66.654545454545328</v>
+        <v>-66.543999999999997</v>
       </c>
       <c r="H26" s="6">
         <f t="shared" si="35"/>
@@ -8629,7 +8633,7 @@
       </c>
       <c r="I26" s="6">
         <f t="shared" ref="I26" si="97">G26</f>
-        <v>-66.654545454545328</v>
+        <v>-66.543999999999997</v>
       </c>
       <c r="K26" s="6">
         <f t="shared" si="28"/>
@@ -8640,14 +8644,14 @@
       </c>
       <c r="M26" s="6">
         <f>M25+L5</f>
-        <v>6631.4400000000041</v>
+        <v>6624.5999999999931</v>
       </c>
       <c r="N26" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O26" s="6">
         <f t="shared" si="12"/>
-        <v>6631.4400000000041</v>
+        <v>6624.5999999999931</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="13"/>
@@ -8655,7 +8659,7 @@
       </c>
       <c r="Q26" s="6">
         <f t="shared" si="14"/>
-        <v>-66.524000000000001</v>
+        <v>-66.40999999999984</v>
       </c>
       <c r="R26" s="6">
         <f t="shared" si="29"/>
@@ -8663,7 +8667,7 @@
       </c>
       <c r="S26" s="6">
         <f t="shared" ref="S26" si="98">Q26</f>
-        <v>-66.524000000000001</v>
+        <v>-66.40999999999984</v>
       </c>
     </row>
     <row r="27" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8676,14 +8680,14 @@
       </c>
       <c r="C27" s="6">
         <f>C26+B6</f>
-        <v>6640.6545454545385</v>
+        <v>6633.6533333333327</v>
       </c>
       <c r="D27" s="6">
         <v>4314</v>
       </c>
       <c r="E27" s="6">
         <f t="shared" si="24"/>
-        <v>6640.6545454545385</v>
+        <v>6633.6533333333327</v>
       </c>
       <c r="F27" s="6">
         <f t="shared" si="25"/>
@@ -8691,7 +8695,7 @@
       </c>
       <c r="G27" s="6">
         <f t="shared" si="26"/>
-        <v>-66.677575757575667</v>
+        <v>-66.56088888888884</v>
       </c>
       <c r="H27" s="6">
         <f t="shared" si="35"/>
@@ -8699,7 +8703,7 @@
       </c>
       <c r="I27" s="6">
         <f t="shared" ref="I27" si="99">G27</f>
-        <v>-66.677575757575667</v>
+        <v>-66.56088888888884</v>
       </c>
       <c r="K27" s="6">
         <f t="shared" si="28"/>
@@ -8710,14 +8714,14 @@
       </c>
       <c r="M27" s="6">
         <f>M26+L5</f>
-        <v>6632.7000000000044</v>
+        <v>6625.4999999999927</v>
       </c>
       <c r="N27" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O27" s="6">
         <f t="shared" si="12"/>
-        <v>6632.7000000000044</v>
+        <v>6625.4999999999927</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="13"/>
@@ -8725,7 +8729,7 @@
       </c>
       <c r="Q27" s="6">
         <f t="shared" si="14"/>
-        <v>-66.545000000000002</v>
+        <v>-66.424999999999827</v>
       </c>
       <c r="R27" s="6">
         <f t="shared" si="29"/>
@@ -8733,7 +8737,7 @@
       </c>
       <c r="S27" s="6">
         <f t="shared" ref="S27" si="100">Q27</f>
-        <v>-66.545000000000002</v>
+        <v>-66.424999999999827</v>
       </c>
     </row>
     <row r="28" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8746,14 +8750,14 @@
       </c>
       <c r="C28" s="6">
         <f>C27+B6</f>
-        <v>6642.0363636363563</v>
+        <v>6634.6666666666661</v>
       </c>
       <c r="D28" s="6">
         <v>4314</v>
       </c>
       <c r="E28" s="6">
         <f t="shared" si="24"/>
-        <v>6642.0363636363563</v>
+        <v>6634.6666666666661</v>
       </c>
       <c r="F28" s="6">
         <f t="shared" si="25"/>
@@ -8761,7 +8765,7 @@
       </c>
       <c r="G28" s="6">
         <f t="shared" si="26"/>
-        <v>-66.700606060606006</v>
+        <v>-66.57777777777784</v>
       </c>
       <c r="H28" s="6">
         <f t="shared" si="35"/>
@@ -8769,7 +8773,7 @@
       </c>
       <c r="I28" s="6">
         <f t="shared" ref="I28" si="101">G28</f>
-        <v>-66.700606060606006</v>
+        <v>-66.57777777777784</v>
       </c>
       <c r="K28" s="6">
         <f t="shared" si="28"/>
@@ -8780,14 +8784,14 @@
       </c>
       <c r="M28" s="6">
         <f>M27+L5</f>
-        <v>6633.9600000000046</v>
+        <v>6626.3999999999924</v>
       </c>
       <c r="N28" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O28" s="6">
         <f t="shared" si="12"/>
-        <v>6633.9600000000046</v>
+        <v>6626.3999999999924</v>
       </c>
       <c r="P28" s="6">
         <f t="shared" si="13"/>
@@ -8795,7 +8799,7 @@
       </c>
       <c r="Q28" s="6">
         <f t="shared" si="14"/>
-        <v>-66.566000000000003</v>
+        <v>-66.439999999999827</v>
       </c>
       <c r="R28" s="6">
         <f t="shared" si="29"/>
@@ -8803,7 +8807,7 @@
       </c>
       <c r="S28" s="6">
         <f t="shared" ref="S28" si="102">Q28</f>
-        <v>-66.566000000000003</v>
+        <v>-66.439999999999827</v>
       </c>
     </row>
     <row r="29" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8816,14 +8820,14 @@
       </c>
       <c r="C29" s="6">
         <f>C28+B6</f>
-        <v>6643.4181818181742</v>
+        <v>6635.6799999999994</v>
       </c>
       <c r="D29" s="6">
         <v>4314</v>
       </c>
       <c r="E29" s="6">
         <f t="shared" si="24"/>
-        <v>6643.4181818181742</v>
+        <v>6635.6799999999994</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="25"/>
@@ -8831,7 +8835,7 @@
       </c>
       <c r="G29" s="6">
         <f t="shared" si="26"/>
-        <v>-66.72363636363616</v>
+        <v>-66.594666666666669</v>
       </c>
       <c r="H29" s="6">
         <f t="shared" si="35"/>
@@ -8839,7 +8843,7 @@
       </c>
       <c r="I29" s="6">
         <f t="shared" ref="I29" si="103">G29</f>
-        <v>-66.72363636363616</v>
+        <v>-66.594666666666669</v>
       </c>
       <c r="K29" s="6">
         <f t="shared" si="28"/>
@@ -8850,14 +8854,14 @@
       </c>
       <c r="M29" s="6">
         <f>M28+L5</f>
-        <v>6635.2200000000048</v>
+        <v>6627.299999999992</v>
       </c>
       <c r="N29" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O29" s="6">
         <f t="shared" si="12"/>
-        <v>6635.2200000000048</v>
+        <v>6627.299999999992</v>
       </c>
       <c r="P29" s="6">
         <f t="shared" si="13"/>
@@ -8865,7 +8869,7 @@
       </c>
       <c r="Q29" s="6">
         <f t="shared" si="14"/>
-        <v>-66.587000000000003</v>
+        <v>-66.454999999999828</v>
       </c>
       <c r="R29" s="6">
         <f t="shared" si="29"/>
@@ -8873,7 +8877,7 @@
       </c>
       <c r="S29" s="6">
         <f t="shared" ref="S29" si="104">Q29</f>
-        <v>-66.587000000000003</v>
+        <v>-66.454999999999828</v>
       </c>
     </row>
     <row r="30" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8886,14 +8890,14 @@
       </c>
       <c r="C30" s="6">
         <f>C29+B6</f>
-        <v>6644.799999999992</v>
+        <v>6636.6933333333327</v>
       </c>
       <c r="D30" s="6">
         <v>4314</v>
       </c>
       <c r="E30" s="6">
         <f t="shared" si="24"/>
-        <v>6644.799999999992</v>
+        <v>6636.6933333333327</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" si="25"/>
@@ -8901,7 +8905,7 @@
       </c>
       <c r="G30" s="6">
         <f t="shared" si="26"/>
-        <v>-66.746666666666499</v>
+        <v>-66.611555555555498</v>
       </c>
       <c r="H30" s="6">
         <f t="shared" si="35"/>
@@ -8909,7 +8913,7 @@
       </c>
       <c r="I30" s="6">
         <f t="shared" ref="I30" si="105">G30</f>
-        <v>-66.746666666666499</v>
+        <v>-66.611555555555498</v>
       </c>
       <c r="K30" s="6">
         <f t="shared" si="28"/>
@@ -8920,14 +8924,14 @@
       </c>
       <c r="M30" s="6">
         <f>M29+L5</f>
-        <v>6636.480000000005</v>
+        <v>6628.1999999999916</v>
       </c>
       <c r="N30" s="6">
         <v>4314.8500000000004</v>
       </c>
       <c r="O30" s="6">
         <f t="shared" si="12"/>
-        <v>6636.480000000005</v>
+        <v>6628.1999999999916</v>
       </c>
       <c r="P30" s="6">
         <f t="shared" si="13"/>
@@ -8935,7 +8939,7 @@
       </c>
       <c r="Q30" s="6">
         <f t="shared" si="14"/>
-        <v>-66.60800000000016</v>
+        <v>-66.469999999999828</v>
       </c>
       <c r="R30" s="6">
         <f t="shared" si="29"/>
@@ -8943,7 +8947,7 @@
       </c>
       <c r="S30" s="6">
         <f t="shared" ref="S30" si="106">Q30</f>
-        <v>-66.60800000000016</v>
+        <v>-66.469999999999828</v>
       </c>
     </row>
     <row r="31" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8956,14 +8960,14 @@
       </c>
       <c r="C31" s="6">
         <f>C30+B6</f>
-        <v>6646.1818181818098</v>
+        <v>6637.706666666666</v>
       </c>
       <c r="D31" s="6">
         <v>4314</v>
       </c>
       <c r="E31" s="6">
         <f t="shared" si="24"/>
-        <v>6646.1818181818098</v>
+        <v>6637.706666666666</v>
       </c>
       <c r="F31" s="6">
         <f t="shared" si="25"/>
@@ -8971,7 +8975,7 @@
       </c>
       <c r="G31" s="6">
         <f t="shared" si="26"/>
-        <v>-66.769696969696838</v>
+        <v>-66.628444444444497</v>
       </c>
       <c r="H31" s="6">
         <f t="shared" si="35"/>
@@ -8979,7 +8983,7 @@
       </c>
       <c r="I31" s="6">
         <f t="shared" ref="I31" si="107">G31</f>
-        <v>-66.769696969696838</v>
+        <v>-66.628444444444497</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>30</v>
